--- a/public/informes-templates/INFORME SEVOMOTOR .xlsx
+++ b/public/informes-templates/INFORME SEVOMOTOR .xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235D9DF4-17C1-4826-B215-89B85B729886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE89842-481F-4A85-9C00-A06F8C1D1562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,25 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="170">
-  <si>
-    <t>INFORME DE SERVICIO</t>
-  </si>
-  <si>
-    <t>EMPRESA / CLIENTE</t>
-  </si>
-  <si>
-    <t>CONTACTO</t>
-  </si>
-  <si>
-    <t>ORDEN DE COMPRA</t>
-  </si>
-  <si>
-    <t>COT</t>
-  </si>
-  <si>
-    <t>LINEA / AREA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="162">
   <si>
     <t xml:space="preserve">DESCRIPCION </t>
   </si>
@@ -44,12 +26,6 @@
     <t>CANTIDAD</t>
   </si>
   <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EQUIPO 1 </t>
-  </si>
-  <si>
     <t>DATOS DEL EQUIPO</t>
   </si>
   <si>
@@ -71,9 +47,6 @@
     <t>RPM</t>
   </si>
   <si>
-    <t>SN</t>
-  </si>
-  <si>
     <t>OPERARIO</t>
   </si>
   <si>
@@ -525,6 +498,9 @@
   </si>
   <si>
     <t>RECOMENDACIONES</t>
+  </si>
+  <si>
+    <t>S/N</t>
   </si>
 </sst>
 </file>
@@ -559,22 +535,8 @@
     <font>
       <b/>
       <i/>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="20"/>
-      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -688,8 +650,21 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -718,6 +693,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -964,15 +945,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -981,67 +959,67 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1059,22 +1037,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1083,59 +1070,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1143,101 +1088,200 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1262,7 +1306,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>103</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="95250" cy="276225"/>
@@ -1297,50 +1341,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1545,24 +1545,24 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z489"/>
+  <dimension ref="A1:Z486"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="50"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -1582,15 +1582,15 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="54"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="36"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1610,17 +1610,15 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="82"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="39"/>
+      <c r="A3" s="91"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="93"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1640,17 +1638,15 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="67"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="39"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="41"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1669,27 +1665,27 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="3" t="s">
+    <row r="5" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="39"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="80"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
@@ -1700,26 +1696,38 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="39"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="76" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="77"/>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="94" t="s">
+        <v>161</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
@@ -1730,26 +1738,24 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="39"/>
+      <c r="A7" s="83"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -1760,26 +1766,28 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="39"/>
+      <c r="A8" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="77"/>
+      <c r="C8" s="76" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="77"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
@@ -1790,26 +1798,24 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="67"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="39"/>
+      <c r="A9" s="85"/>
+      <c r="B9" s="86"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="90"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
@@ -1820,17 +1826,19 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="67"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="39"/>
+      <c r="A10" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1850,17 +1858,19 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="53"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="67"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="39"/>
+      <c r="A11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="26"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1880,15 +1890,19 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="39"/>
+      <c r="A12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="28"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1908,28 +1922,28 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="71" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="66" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="39"/>
+      <c r="A13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="28"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
@@ -1939,39 +1953,29 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="51"/>
-      <c r="B14" s="52"/>
-      <c r="C14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="3" t="s">
+    <row r="14" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="28"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
@@ -1982,24 +1986,28 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="51"/>
-      <c r="B15" s="52"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
+      <c r="A15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="28"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
@@ -2010,28 +2018,28 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="51"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="3" t="s">
+      <c r="A16" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="66" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="39"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="9"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="28"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
@@ -2042,24 +2050,28 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="53"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
+      <c r="A17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="9"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="28"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
@@ -2070,19 +2082,19 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="73" t="s">
+      <c r="A18" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="74"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="74"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="45"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="28"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -2102,19 +2114,15 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="75"/>
-      <c r="F19" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="28"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -2134,19 +2142,19 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="29"/>
+      <c r="A20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="9"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="28"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -2166,19 +2174,19 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="29"/>
+      <c r="A21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="9"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="28"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -2197,20 +2205,20 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="29"/>
+    <row r="22" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="9"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="28"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -2229,20 +2237,20 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="29"/>
+    <row r="23" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="9"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="30"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -2262,19 +2270,23 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="33"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="41"/>
+      <c r="H24" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="29"/>
+      <c r="I24" s="33"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -2294,19 +2306,15 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="29"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="36"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -2325,20 +2333,16 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="75"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="G26" s="75"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="29"/>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A26" s="52"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="41"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -2358,15 +2362,17 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="59"/>
-      <c r="B27" s="59"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="29"/>
+      <c r="A27" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="41"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -2386,19 +2392,19 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="29"/>
+      <c r="A28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -2418,19 +2424,15 @@
       <c r="Z28" s="1"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" s="10"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="29"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="41"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -2450,19 +2452,15 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G30" s="10"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="29"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="41"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -2481,20 +2479,16 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G31" s="10"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="31"/>
+    <row r="31" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="41"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -2514,23 +2508,15 @@
       <c r="Z31" s="1"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="77" t="s">
-        <v>35</v>
-      </c>
+      <c r="A32" s="10"/>
       <c r="B32" s="39"/>
-      <c r="C32" s="78" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="50"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="77" t="s">
-        <v>35</v>
-      </c>
-      <c r="G32" s="39"/>
-      <c r="H32" s="78" t="s">
-        <v>37</v>
-      </c>
-      <c r="I32" s="50"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="41"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -2550,15 +2536,17 @@
       <c r="Z32" s="1"/>
     </row>
     <row r="33" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="79"/>
-      <c r="B33" s="54"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="79"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="54"/>
+      <c r="A33" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="41"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -2577,16 +2565,20 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A34" s="65"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="39"/>
+    <row r="34" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -2606,17 +2598,17 @@
       <c r="Z34" s="1"/>
     </row>
     <row r="35" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="39"/>
+      <c r="A35" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="12"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -2636,19 +2628,17 @@
       <c r="Z35" s="1"/>
     </row>
     <row r="36" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="66" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="39"/>
+      <c r="A36" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="40"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="12"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -2668,15 +2658,17 @@
       <c r="Z36" s="1"/>
     </row>
     <row r="37" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="11"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="39"/>
+      <c r="A37" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="40"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="12"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -2696,15 +2688,17 @@
       <c r="Z37" s="1"/>
     </row>
     <row r="38" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="11"/>
-      <c r="B38" s="67"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="39"/>
+      <c r="A38" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="40"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="12"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -2724,15 +2718,17 @@
       <c r="Z38" s="1"/>
     </row>
     <row r="39" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="11"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="39"/>
+      <c r="A39" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="40"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="12"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -2752,15 +2748,17 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="11"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="39"/>
+      <c r="A40" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="40"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="12"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -2780,17 +2778,17 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="68" t="s">
+      <c r="A41" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="38"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="39"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="12"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -2809,20 +2807,18 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="69" t="s">
+    <row r="42" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="38"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="12" t="s">
-        <v>42</v>
-      </c>
+      <c r="B42" s="40"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="12"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -2842,17 +2838,17 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="13"/>
+      <c r="A43" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="40"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="12"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -2872,17 +2868,17 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="61" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="38"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="13"/>
+      <c r="A44" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="40"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="12"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -2902,17 +2898,17 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="38"/>
-      <c r="C45" s="38"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="13"/>
+      <c r="A45" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="40"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="12"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -2932,17 +2928,17 @@
       <c r="Z45" s="1"/>
     </row>
     <row r="46" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="61" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46" s="38"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="39"/>
-      <c r="I46" s="13"/>
+      <c r="A46" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="40"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="12"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -2962,17 +2958,17 @@
       <c r="Z46" s="1"/>
     </row>
     <row r="47" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47" s="38"/>
-      <c r="C47" s="38"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="39"/>
-      <c r="I47" s="13"/>
+      <c r="A47" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="40"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="40"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="12"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -2992,17 +2988,17 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" s="38"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="39"/>
-      <c r="I48" s="13"/>
+      <c r="A48" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="40"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="12"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -3022,17 +3018,17 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="61" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="38"/>
-      <c r="C49" s="38"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="39"/>
-      <c r="I49" s="13"/>
+      <c r="A49" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" s="40"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="12"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -3052,17 +3048,17 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50" s="38"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="39"/>
-      <c r="I50" s="13"/>
+      <c r="A50" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="40"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="12"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -3082,17 +3078,17 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="61" t="s">
-        <v>51</v>
-      </c>
-      <c r="B51" s="38"/>
-      <c r="C51" s="38"/>
-      <c r="D51" s="38"/>
-      <c r="E51" s="38"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="39"/>
-      <c r="I51" s="13"/>
+      <c r="A51" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="40"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="12"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -3112,17 +3108,17 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="61" t="s">
-        <v>52</v>
-      </c>
-      <c r="B52" s="38"/>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="13"/>
+      <c r="A52" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="40"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="12"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -3142,17 +3138,17 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="61" t="s">
-        <v>53</v>
-      </c>
-      <c r="B53" s="38"/>
-      <c r="C53" s="38"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="13"/>
+      <c r="A53" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="40"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="40"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="12"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -3172,17 +3168,17 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54" s="38"/>
-      <c r="C54" s="38"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="13"/>
+      <c r="A54" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="40"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="12"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -3202,17 +3198,17 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55" s="38"/>
-      <c r="C55" s="38"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="13"/>
+      <c r="A55" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="40"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="12"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -3232,17 +3228,17 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B56" s="38"/>
-      <c r="C56" s="38"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="13"/>
+      <c r="A56" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="40"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="40"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="12"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -3262,17 +3258,19 @@
       <c r="Z56" s="1"/>
     </row>
     <row r="57" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="61" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57" s="38"/>
-      <c r="C57" s="38"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="39"/>
-      <c r="I57" s="13"/>
+      <c r="A57" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="40"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -3292,17 +3290,17 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="61" t="s">
-        <v>58</v>
-      </c>
-      <c r="B58" s="38"/>
-      <c r="C58" s="38"/>
-      <c r="D58" s="38"/>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="39"/>
-      <c r="I58" s="13"/>
+      <c r="A58" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="40"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="41"/>
+      <c r="I58" s="12"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -3322,17 +3320,17 @@
       <c r="Z58" s="1"/>
     </row>
     <row r="59" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="61" t="s">
-        <v>59</v>
-      </c>
-      <c r="B59" s="38"/>
-      <c r="C59" s="38"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="13"/>
+      <c r="A59" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" s="40"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="12"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -3352,17 +3350,17 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="61" t="s">
-        <v>60</v>
-      </c>
-      <c r="B60" s="38"/>
-      <c r="C60" s="38"/>
-      <c r="D60" s="38"/>
-      <c r="E60" s="38"/>
-      <c r="F60" s="38"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="39"/>
-      <c r="I60" s="13"/>
+      <c r="A60" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="40"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="41"/>
+      <c r="I60" s="12"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -3382,17 +3380,17 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="61" t="s">
-        <v>61</v>
-      </c>
-      <c r="B61" s="38"/>
-      <c r="C61" s="38"/>
-      <c r="D61" s="38"/>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="39"/>
-      <c r="I61" s="13"/>
+      <c r="A61" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="40"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="40"/>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40"/>
+      <c r="G61" s="40"/>
+      <c r="H61" s="41"/>
+      <c r="I61" s="12"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -3412,17 +3410,17 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="B62" s="38"/>
-      <c r="C62" s="38"/>
-      <c r="D62" s="38"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="39"/>
-      <c r="I62" s="13"/>
+      <c r="A62" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="40"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40"/>
+      <c r="G62" s="40"/>
+      <c r="H62" s="41"/>
+      <c r="I62" s="12"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -3442,17 +3440,17 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="61" t="s">
-        <v>63</v>
-      </c>
-      <c r="B63" s="38"/>
-      <c r="C63" s="38"/>
-      <c r="D63" s="38"/>
-      <c r="E63" s="38"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="39"/>
-      <c r="I63" s="13"/>
+      <c r="A63" s="56" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="40"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="40"/>
+      <c r="E63" s="40"/>
+      <c r="F63" s="40"/>
+      <c r="G63" s="40"/>
+      <c r="H63" s="41"/>
+      <c r="I63" s="12"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -3472,17 +3470,17 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="B64" s="38"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="39"/>
-      <c r="I64" s="13"/>
+      <c r="A64" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="40"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="40"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="40"/>
+      <c r="H64" s="41"/>
+      <c r="I64" s="12"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -3502,19 +3500,17 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="B65" s="38"/>
-      <c r="C65" s="38"/>
-      <c r="D65" s="38"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="38"/>
-      <c r="G65" s="39"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="12" t="s">
-        <v>42</v>
-      </c>
+      <c r="A65" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" s="40"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="40"/>
+      <c r="F65" s="40"/>
+      <c r="G65" s="40"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="12"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -3534,17 +3530,17 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="B66" s="38"/>
-      <c r="C66" s="38"/>
-      <c r="D66" s="38"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="38"/>
-      <c r="G66" s="38"/>
-      <c r="H66" s="39"/>
-      <c r="I66" s="13"/>
+      <c r="A66" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="41"/>
+      <c r="I66" s="12"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -3564,17 +3560,17 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="61" t="s">
-        <v>67</v>
-      </c>
-      <c r="B67" s="38"/>
-      <c r="C67" s="38"/>
-      <c r="D67" s="38"/>
-      <c r="E67" s="38"/>
-      <c r="F67" s="38"/>
-      <c r="G67" s="38"/>
-      <c r="H67" s="39"/>
-      <c r="I67" s="13"/>
+      <c r="A67" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="40"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="40"/>
+      <c r="F67" s="40"/>
+      <c r="G67" s="40"/>
+      <c r="H67" s="41"/>
+      <c r="I67" s="12"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
@@ -3594,17 +3590,17 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="B68" s="38"/>
-      <c r="C68" s="38"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="38"/>
-      <c r="G68" s="38"/>
-      <c r="H68" s="39"/>
-      <c r="I68" s="13"/>
+      <c r="A68" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="40"/>
+      <c r="C68" s="40"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="40"/>
+      <c r="F68" s="40"/>
+      <c r="G68" s="40"/>
+      <c r="H68" s="41"/>
+      <c r="I68" s="12"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -3624,17 +3620,17 @@
       <c r="Z68" s="1"/>
     </row>
     <row r="69" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="61" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69" s="38"/>
-      <c r="C69" s="38"/>
-      <c r="D69" s="38"/>
-      <c r="E69" s="38"/>
-      <c r="F69" s="38"/>
-      <c r="G69" s="38"/>
-      <c r="H69" s="39"/>
-      <c r="I69" s="13"/>
+      <c r="A69" s="56" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" s="40"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="40"/>
+      <c r="F69" s="40"/>
+      <c r="G69" s="40"/>
+      <c r="H69" s="41"/>
+      <c r="I69" s="12"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
@@ -3654,17 +3650,17 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="61" t="s">
-        <v>70</v>
-      </c>
-      <c r="B70" s="38"/>
-      <c r="C70" s="38"/>
-      <c r="D70" s="38"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="38"/>
-      <c r="G70" s="38"/>
-      <c r="H70" s="39"/>
-      <c r="I70" s="13"/>
+      <c r="A70" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="40"/>
+      <c r="C70" s="40"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="40"/>
+      <c r="H70" s="41"/>
+      <c r="I70" s="12"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
@@ -3684,17 +3680,17 @@
       <c r="Z70" s="1"/>
     </row>
     <row r="71" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="61" t="s">
-        <v>71</v>
-      </c>
-      <c r="B71" s="38"/>
-      <c r="C71" s="38"/>
-      <c r="D71" s="38"/>
-      <c r="E71" s="38"/>
-      <c r="F71" s="38"/>
-      <c r="G71" s="38"/>
-      <c r="H71" s="39"/>
-      <c r="I71" s="13"/>
+      <c r="A71" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="40"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="40"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="40"/>
+      <c r="G71" s="40"/>
+      <c r="H71" s="41"/>
+      <c r="I71" s="12"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -3714,17 +3710,17 @@
       <c r="Z71" s="1"/>
     </row>
     <row r="72" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="B72" s="38"/>
-      <c r="C72" s="38"/>
-      <c r="D72" s="38"/>
-      <c r="E72" s="38"/>
-      <c r="F72" s="38"/>
-      <c r="G72" s="38"/>
-      <c r="H72" s="39"/>
-      <c r="I72" s="13"/>
+      <c r="A72" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" s="40"/>
+      <c r="C72" s="40"/>
+      <c r="D72" s="40"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="40"/>
+      <c r="G72" s="40"/>
+      <c r="H72" s="41"/>
+      <c r="I72" s="12"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -3744,17 +3740,17 @@
       <c r="Z72" s="1"/>
     </row>
     <row r="73" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="B73" s="38"/>
-      <c r="C73" s="38"/>
-      <c r="D73" s="38"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="38"/>
-      <c r="G73" s="38"/>
-      <c r="H73" s="39"/>
-      <c r="I73" s="13"/>
+      <c r="A73" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73" s="40"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="40"/>
+      <c r="F73" s="40"/>
+      <c r="G73" s="40"/>
+      <c r="H73" s="41"/>
+      <c r="I73" s="12"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
@@ -3774,17 +3770,17 @@
       <c r="Z73" s="1"/>
     </row>
     <row r="74" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="B74" s="38"/>
-      <c r="C74" s="38"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="38"/>
-      <c r="G74" s="38"/>
-      <c r="H74" s="39"/>
-      <c r="I74" s="13"/>
+      <c r="A74" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74" s="40"/>
+      <c r="C74" s="40"/>
+      <c r="D74" s="40"/>
+      <c r="E74" s="40"/>
+      <c r="F74" s="40"/>
+      <c r="G74" s="40"/>
+      <c r="H74" s="41"/>
+      <c r="I74" s="12"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
@@ -3804,17 +3800,17 @@
       <c r="Z74" s="1"/>
     </row>
     <row r="75" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="61" t="s">
-        <v>75</v>
-      </c>
-      <c r="B75" s="38"/>
-      <c r="C75" s="38"/>
-      <c r="D75" s="38"/>
-      <c r="E75" s="38"/>
-      <c r="F75" s="38"/>
-      <c r="G75" s="38"/>
-      <c r="H75" s="39"/>
-      <c r="I75" s="13"/>
+      <c r="A75" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75" s="40"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="40"/>
+      <c r="E75" s="40"/>
+      <c r="F75" s="40"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="41"/>
+      <c r="I75" s="12"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
@@ -3834,17 +3830,17 @@
       <c r="Z75" s="1"/>
     </row>
     <row r="76" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="B76" s="38"/>
-      <c r="C76" s="38"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="38"/>
-      <c r="H76" s="39"/>
-      <c r="I76" s="13"/>
+      <c r="A76" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76" s="40"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="41"/>
+      <c r="I76" s="12"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -3864,17 +3860,17 @@
       <c r="Z76" s="1"/>
     </row>
     <row r="77" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="B77" s="38"/>
-      <c r="C77" s="38"/>
-      <c r="D77" s="38"/>
-      <c r="E77" s="38"/>
-      <c r="F77" s="38"/>
-      <c r="G77" s="38"/>
-      <c r="H77" s="39"/>
-      <c r="I77" s="13"/>
+      <c r="A77" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77" s="40"/>
+      <c r="C77" s="40"/>
+      <c r="D77" s="40"/>
+      <c r="E77" s="40"/>
+      <c r="F77" s="40"/>
+      <c r="G77" s="40"/>
+      <c r="H77" s="41"/>
+      <c r="I77" s="12"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -3894,17 +3890,17 @@
       <c r="Z77" s="1"/>
     </row>
     <row r="78" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="61" t="s">
-        <v>78</v>
-      </c>
-      <c r="B78" s="38"/>
-      <c r="C78" s="38"/>
-      <c r="D78" s="38"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="38"/>
-      <c r="H78" s="39"/>
-      <c r="I78" s="13"/>
+      <c r="A78" s="56" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78" s="40"/>
+      <c r="C78" s="40"/>
+      <c r="D78" s="40"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
+      <c r="G78" s="40"/>
+      <c r="H78" s="41"/>
+      <c r="I78" s="12"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
@@ -3924,17 +3920,19 @@
       <c r="Z78" s="1"/>
     </row>
     <row r="79" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="B79" s="38"/>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="39"/>
-      <c r="I79" s="13"/>
+      <c r="A79" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
@@ -3954,17 +3952,17 @@
       <c r="Z79" s="1"/>
     </row>
     <row r="80" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="61" t="s">
-        <v>80</v>
-      </c>
-      <c r="B80" s="38"/>
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="39"/>
-      <c r="I80" s="13"/>
+      <c r="A80" s="56" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="12"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
@@ -3984,17 +3982,17 @@
       <c r="Z80" s="1"/>
     </row>
     <row r="81" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="B81" s="38"/>
-      <c r="C81" s="38"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="38"/>
-      <c r="F81" s="38"/>
-      <c r="G81" s="38"/>
-      <c r="H81" s="39"/>
-      <c r="I81" s="13"/>
+      <c r="A81" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81" s="40"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="40"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="40"/>
+      <c r="G81" s="40"/>
+      <c r="H81" s="41"/>
+      <c r="I81" s="12"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
@@ -4014,17 +4012,17 @@
       <c r="Z81" s="1"/>
     </row>
     <row r="82" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="61" t="s">
-        <v>82</v>
-      </c>
-      <c r="B82" s="38"/>
-      <c r="C82" s="38"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="38"/>
-      <c r="F82" s="38"/>
-      <c r="G82" s="38"/>
-      <c r="H82" s="39"/>
-      <c r="I82" s="13"/>
+      <c r="A82" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="B82" s="40"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="40"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="40"/>
+      <c r="H82" s="41"/>
+      <c r="I82" s="12"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
@@ -4044,17 +4042,17 @@
       <c r="Z82" s="1"/>
     </row>
     <row r="83" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="61" t="s">
-        <v>83</v>
-      </c>
-      <c r="B83" s="38"/>
-      <c r="C83" s="38"/>
-      <c r="D83" s="38"/>
-      <c r="E83" s="38"/>
-      <c r="F83" s="38"/>
-      <c r="G83" s="38"/>
-      <c r="H83" s="39"/>
-      <c r="I83" s="13"/>
+      <c r="A83" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B83" s="40"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="40"/>
+      <c r="E83" s="40"/>
+      <c r="F83" s="40"/>
+      <c r="G83" s="40"/>
+      <c r="H83" s="41"/>
+      <c r="I83" s="12"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
@@ -4074,17 +4072,17 @@
       <c r="Z83" s="1"/>
     </row>
     <row r="84" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="B84" s="38"/>
-      <c r="C84" s="38"/>
-      <c r="D84" s="38"/>
-      <c r="E84" s="38"/>
-      <c r="F84" s="38"/>
-      <c r="G84" s="38"/>
-      <c r="H84" s="39"/>
-      <c r="I84" s="13"/>
+      <c r="A84" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="B84" s="40"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="40"/>
+      <c r="E84" s="40"/>
+      <c r="F84" s="40"/>
+      <c r="G84" s="40"/>
+      <c r="H84" s="41"/>
+      <c r="I84" s="12"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
@@ -4104,17 +4102,17 @@
       <c r="Z84" s="1"/>
     </row>
     <row r="85" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="61" t="s">
-        <v>85</v>
-      </c>
-      <c r="B85" s="38"/>
-      <c r="C85" s="38"/>
-      <c r="D85" s="38"/>
-      <c r="E85" s="38"/>
-      <c r="F85" s="38"/>
-      <c r="G85" s="38"/>
-      <c r="H85" s="39"/>
-      <c r="I85" s="13"/>
+      <c r="A85" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="B85" s="40"/>
+      <c r="C85" s="40"/>
+      <c r="D85" s="40"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="40"/>
+      <c r="H85" s="41"/>
+      <c r="I85" s="12"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
@@ -4134,17 +4132,17 @@
       <c r="Z85" s="1"/>
     </row>
     <row r="86" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="61" t="s">
-        <v>86</v>
-      </c>
-      <c r="B86" s="38"/>
-      <c r="C86" s="38"/>
-      <c r="D86" s="38"/>
-      <c r="E86" s="38"/>
-      <c r="F86" s="38"/>
-      <c r="G86" s="38"/>
-      <c r="H86" s="39"/>
-      <c r="I86" s="13"/>
+      <c r="A86" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="B86" s="40"/>
+      <c r="C86" s="40"/>
+      <c r="D86" s="40"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="40"/>
+      <c r="G86" s="40"/>
+      <c r="H86" s="41"/>
+      <c r="I86" s="12"/>
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
@@ -4164,19 +4162,17 @@
       <c r="Z86" s="1"/>
     </row>
     <row r="87" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="B87" s="38"/>
-      <c r="C87" s="38"/>
-      <c r="D87" s="38"/>
-      <c r="E87" s="38"/>
-      <c r="F87" s="38"/>
-      <c r="G87" s="39"/>
-      <c r="H87" s="14"/>
-      <c r="I87" s="12" t="s">
-        <v>42</v>
-      </c>
+      <c r="A87" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B87" s="40"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
+      <c r="E87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="40"/>
+      <c r="H87" s="41"/>
+      <c r="I87" s="12"/>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
@@ -4196,17 +4192,17 @@
       <c r="Z87" s="1"/>
     </row>
     <row r="88" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="61" t="s">
-        <v>88</v>
-      </c>
-      <c r="B88" s="38"/>
-      <c r="C88" s="38"/>
-      <c r="D88" s="38"/>
-      <c r="E88" s="38"/>
-      <c r="F88" s="38"/>
-      <c r="G88" s="38"/>
-      <c r="H88" s="39"/>
-      <c r="I88" s="13"/>
+      <c r="A88" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="B88" s="40"/>
+      <c r="C88" s="40"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="41"/>
+      <c r="I88" s="12"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
@@ -4226,17 +4222,17 @@
       <c r="Z88" s="1"/>
     </row>
     <row r="89" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="B89" s="38"/>
-      <c r="C89" s="38"/>
-      <c r="D89" s="38"/>
-      <c r="E89" s="38"/>
-      <c r="F89" s="38"/>
-      <c r="G89" s="38"/>
-      <c r="H89" s="39"/>
-      <c r="I89" s="13"/>
+      <c r="A89" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B89" s="40"/>
+      <c r="C89" s="40"/>
+      <c r="D89" s="40"/>
+      <c r="E89" s="40"/>
+      <c r="F89" s="40"/>
+      <c r="G89" s="40"/>
+      <c r="H89" s="41"/>
+      <c r="I89" s="12"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
@@ -4256,17 +4252,17 @@
       <c r="Z89" s="1"/>
     </row>
     <row r="90" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="B90" s="38"/>
-      <c r="C90" s="38"/>
-      <c r="D90" s="38"/>
-      <c r="E90" s="38"/>
-      <c r="F90" s="38"/>
-      <c r="G90" s="38"/>
-      <c r="H90" s="39"/>
-      <c r="I90" s="13"/>
+      <c r="A90" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="B90" s="40"/>
+      <c r="C90" s="40"/>
+      <c r="D90" s="40"/>
+      <c r="E90" s="40"/>
+      <c r="F90" s="40"/>
+      <c r="G90" s="40"/>
+      <c r="H90" s="41"/>
+      <c r="I90" s="12"/>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
@@ -4286,17 +4282,17 @@
       <c r="Z90" s="1"/>
     </row>
     <row r="91" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="B91" s="38"/>
-      <c r="C91" s="38"/>
-      <c r="D91" s="38"/>
-      <c r="E91" s="38"/>
-      <c r="F91" s="38"/>
-      <c r="G91" s="38"/>
-      <c r="H91" s="39"/>
-      <c r="I91" s="13"/>
+      <c r="A91" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="B91" s="40"/>
+      <c r="C91" s="40"/>
+      <c r="D91" s="40"/>
+      <c r="E91" s="40"/>
+      <c r="F91" s="40"/>
+      <c r="G91" s="40"/>
+      <c r="H91" s="41"/>
+      <c r="I91" s="12"/>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
@@ -4316,17 +4312,17 @@
       <c r="Z91" s="1"/>
     </row>
     <row r="92" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="B92" s="38"/>
-      <c r="C92" s="38"/>
-      <c r="D92" s="38"/>
-      <c r="E92" s="38"/>
-      <c r="F92" s="38"/>
-      <c r="G92" s="38"/>
-      <c r="H92" s="39"/>
-      <c r="I92" s="13"/>
+      <c r="A92" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="B92" s="40"/>
+      <c r="C92" s="40"/>
+      <c r="D92" s="40"/>
+      <c r="E92" s="40"/>
+      <c r="F92" s="40"/>
+      <c r="G92" s="40"/>
+      <c r="H92" s="41"/>
+      <c r="I92" s="12"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
@@ -4346,17 +4342,17 @@
       <c r="Z92" s="1"/>
     </row>
     <row r="93" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="B93" s="38"/>
-      <c r="C93" s="38"/>
-      <c r="D93" s="38"/>
-      <c r="E93" s="38"/>
-      <c r="F93" s="38"/>
-      <c r="G93" s="38"/>
-      <c r="H93" s="39"/>
-      <c r="I93" s="13"/>
+      <c r="A93" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="B93" s="40"/>
+      <c r="C93" s="40"/>
+      <c r="D93" s="40"/>
+      <c r="E93" s="40"/>
+      <c r="F93" s="40"/>
+      <c r="G93" s="40"/>
+      <c r="H93" s="41"/>
+      <c r="I93" s="12"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
@@ -4376,17 +4372,17 @@
       <c r="Z93" s="1"/>
     </row>
     <row r="94" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="B94" s="38"/>
-      <c r="C94" s="38"/>
-      <c r="D94" s="38"/>
-      <c r="E94" s="38"/>
-      <c r="F94" s="38"/>
-      <c r="G94" s="38"/>
-      <c r="H94" s="39"/>
-      <c r="I94" s="13"/>
+      <c r="A94" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" s="40"/>
+      <c r="C94" s="40"/>
+      <c r="D94" s="40"/>
+      <c r="E94" s="40"/>
+      <c r="F94" s="40"/>
+      <c r="G94" s="40"/>
+      <c r="H94" s="41"/>
+      <c r="I94" s="12"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
@@ -4405,18 +4401,18 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="61" t="s">
-        <v>95</v>
-      </c>
-      <c r="B95" s="38"/>
-      <c r="C95" s="38"/>
-      <c r="D95" s="38"/>
-      <c r="E95" s="38"/>
-      <c r="F95" s="38"/>
-      <c r="G95" s="38"/>
-      <c r="H95" s="39"/>
-      <c r="I95" s="13"/>
+    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="B95" s="41"/>
+      <c r="C95" s="59"/>
+      <c r="D95" s="40"/>
+      <c r="E95" s="40"/>
+      <c r="F95" s="40"/>
+      <c r="G95" s="40"/>
+      <c r="H95" s="40"/>
+      <c r="I95" s="41"/>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
@@ -4436,17 +4432,17 @@
       <c r="Z95" s="1"/>
     </row>
     <row r="96" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="61" t="s">
-        <v>96</v>
-      </c>
-      <c r="B96" s="38"/>
-      <c r="C96" s="38"/>
-      <c r="D96" s="38"/>
-      <c r="E96" s="38"/>
-      <c r="F96" s="38"/>
-      <c r="G96" s="38"/>
-      <c r="H96" s="39"/>
-      <c r="I96" s="13"/>
+      <c r="A96" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="B96" s="40"/>
+      <c r="C96" s="40"/>
+      <c r="D96" s="40"/>
+      <c r="E96" s="40"/>
+      <c r="F96" s="40"/>
+      <c r="G96" s="40"/>
+      <c r="H96" s="40"/>
+      <c r="I96" s="41"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
@@ -4465,18 +4461,22 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="61" t="s">
-        <v>53</v>
-      </c>
-      <c r="B97" s="38"/>
-      <c r="C97" s="38"/>
-      <c r="D97" s="38"/>
-      <c r="E97" s="38"/>
-      <c r="F97" s="38"/>
-      <c r="G97" s="38"/>
-      <c r="H97" s="39"/>
-      <c r="I97" s="13"/>
+        <v>95</v>
+      </c>
+      <c r="B97" s="41"/>
+      <c r="C97" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="D97" s="40"/>
+      <c r="E97" s="41"/>
+      <c r="F97" s="62" t="s">
+        <v>97</v>
+      </c>
+      <c r="G97" s="40"/>
+      <c r="H97" s="40"/>
+      <c r="I97" s="41"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
@@ -4495,18 +4495,28 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B98" s="38"/>
-      <c r="C98" s="38"/>
-      <c r="D98" s="38"/>
-      <c r="E98" s="38"/>
-      <c r="F98" s="38"/>
-      <c r="G98" s="38"/>
-      <c r="H98" s="39"/>
-      <c r="I98" s="13"/>
+    <row r="98" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C98" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D98" s="41"/>
+      <c r="E98" s="63"/>
+      <c r="F98" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="G98" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="H98" s="41"/>
+      <c r="I98" s="15" t="s">
+        <v>102</v>
+      </c>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
@@ -4525,18 +4535,22 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="B99" s="38"/>
-      <c r="C99" s="38"/>
-      <c r="D99" s="38"/>
-      <c r="E99" s="38"/>
-      <c r="F99" s="38"/>
-      <c r="G99" s="38"/>
-      <c r="H99" s="39"/>
-      <c r="I99" s="13"/>
+    <row r="99" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B99" s="16"/>
+      <c r="C99" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D99" s="16"/>
+      <c r="E99" s="46"/>
+      <c r="F99" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G99" s="64"/>
+      <c r="H99" s="41"/>
+      <c r="I99" s="17"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
@@ -4555,18 +4569,22 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="B100" s="38"/>
-      <c r="C100" s="38"/>
-      <c r="D100" s="38"/>
-      <c r="E100" s="38"/>
-      <c r="F100" s="38"/>
-      <c r="G100" s="38"/>
-      <c r="H100" s="39"/>
-      <c r="I100" s="13"/>
+    <row r="100" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" s="16"/>
+      <c r="C100" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D100" s="16"/>
+      <c r="E100" s="46"/>
+      <c r="F100" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="G100" s="64"/>
+      <c r="H100" s="41"/>
+      <c r="I100" s="17"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
@@ -4585,18 +4603,22 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="61" t="s">
-        <v>100</v>
-      </c>
-      <c r="B101" s="38"/>
-      <c r="C101" s="38"/>
-      <c r="D101" s="38"/>
-      <c r="E101" s="38"/>
-      <c r="F101" s="38"/>
-      <c r="G101" s="38"/>
-      <c r="H101" s="39"/>
-      <c r="I101" s="13"/>
+    <row r="101" spans="1:26" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="18"/>
+      <c r="C101" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D101" s="16"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="G101" s="64"/>
+      <c r="H101" s="41"/>
+      <c r="I101" s="17"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -4615,18 +4637,24 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="61" t="s">
-        <v>101</v>
-      </c>
-      <c r="B102" s="38"/>
-      <c r="C102" s="38"/>
-      <c r="D102" s="38"/>
-      <c r="E102" s="38"/>
-      <c r="F102" s="38"/>
-      <c r="G102" s="38"/>
-      <c r="H102" s="39"/>
-      <c r="I102" s="13"/>
+    <row r="102" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C102" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="D102" s="41"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="G102" s="41"/>
+      <c r="H102" s="65"/>
+      <c r="I102" s="41"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -4645,18 +4673,18 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="62" t="s">
-        <v>102</v>
-      </c>
-      <c r="B103" s="39"/>
-      <c r="C103" s="63"/>
-      <c r="D103" s="38"/>
-      <c r="E103" s="38"/>
-      <c r="F103" s="38"/>
-      <c r="G103" s="38"/>
-      <c r="H103" s="38"/>
-      <c r="I103" s="39"/>
+    <row r="103" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B103" s="40"/>
+      <c r="C103" s="40"/>
+      <c r="D103" s="40"/>
+      <c r="E103" s="40"/>
+      <c r="F103" s="40"/>
+      <c r="G103" s="40"/>
+      <c r="H103" s="40"/>
+      <c r="I103" s="41"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -4675,22 +4703,24 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="B104" s="38"/>
-      <c r="C104" s="38"/>
-      <c r="D104" s="38"/>
-      <c r="E104" s="38"/>
-      <c r="F104" s="38"/>
-      <c r="G104" s="38"/>
-      <c r="H104" s="38"/>
-      <c r="I104" s="39"/>
-      <c r="J104" s="1"/>
-      <c r="K104" s="1"/>
-      <c r="L104" s="1"/>
-      <c r="M104" s="1"/>
+    <row r="104" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="B104" s="40"/>
+      <c r="C104" s="41"/>
+      <c r="D104" s="67"/>
+      <c r="E104" s="33"/>
+      <c r="F104" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="G104" s="40"/>
+      <c r="H104" s="40"/>
+      <c r="I104" s="41"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="5"/>
+      <c r="M104" s="5"/>
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
       <c r="P104" s="1"/>
@@ -4705,26 +4735,34 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
     </row>
-    <row r="105" spans="1:26" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="B105" s="39"/>
-      <c r="C105" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="D105" s="38"/>
-      <c r="E105" s="39"/>
-      <c r="F105" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="G105" s="38"/>
-      <c r="H105" s="38"/>
-      <c r="I105" s="39"/>
-      <c r="J105" s="1"/>
-      <c r="K105" s="1"/>
-      <c r="L105" s="1"/>
-      <c r="M105" s="1"/>
+    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A105" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B105" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D105" s="37"/>
+      <c r="E105" s="38"/>
+      <c r="F105" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="G105" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="H105" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I105" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="J105" s="5"/>
+      <c r="K105" s="5"/>
+      <c r="L105" s="5"/>
+      <c r="M105" s="5"/>
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
@@ -4739,32 +4777,24 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row r="106" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B106" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C106" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="D106" s="39"/>
-      <c r="E106" s="57"/>
-      <c r="F106" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G106" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="H106" s="39"/>
-      <c r="I106" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="J106" s="1"/>
-      <c r="K106" s="1"/>
-      <c r="L106" s="1"/>
-      <c r="M106" s="1"/>
+    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A106" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B106" s="16"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="37"/>
+      <c r="E106" s="38"/>
+      <c r="F106" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G106" s="16"/>
+      <c r="H106" s="16"/>
+      <c r="I106" s="16"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5"/>
+      <c r="L106" s="5"/>
+      <c r="M106" s="5"/>
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
       <c r="P106" s="1"/>
@@ -4779,26 +4809,24 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row r="107" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B107" s="17"/>
-      <c r="C107" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D107" s="17"/>
-      <c r="E107" s="58"/>
-      <c r="F107" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="G107" s="60"/>
-      <c r="H107" s="39"/>
-      <c r="I107" s="18"/>
-      <c r="J107" s="1"/>
-      <c r="K107" s="1"/>
-      <c r="L107" s="1"/>
-      <c r="M107" s="1"/>
+    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A107" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B107" s="16"/>
+      <c r="C107" s="16"/>
+      <c r="D107" s="37"/>
+      <c r="E107" s="38"/>
+      <c r="F107" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="G107" s="40"/>
+      <c r="H107" s="40"/>
+      <c r="I107" s="41"/>
+      <c r="J107" s="5"/>
+      <c r="K107" s="5"/>
+      <c r="L107" s="5"/>
+      <c r="M107" s="5"/>
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
       <c r="P107" s="1"/>
@@ -4813,26 +4841,26 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row r="108" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B108" s="17"/>
-      <c r="C108" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D108" s="17"/>
-      <c r="E108" s="58"/>
-      <c r="F108" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G108" s="60"/>
-      <c r="H108" s="39"/>
-      <c r="I108" s="18"/>
-      <c r="J108" s="1"/>
-      <c r="K108" s="1"/>
-      <c r="L108" s="1"/>
-      <c r="M108" s="1"/>
+    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A108" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="B108" s="41"/>
+      <c r="C108" s="21"/>
+      <c r="D108" s="37"/>
+      <c r="E108" s="38"/>
+      <c r="F108" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="G108" s="41"/>
+      <c r="H108" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="I108" s="41"/>
+      <c r="J108" s="5"/>
+      <c r="K108" s="5"/>
+      <c r="L108" s="5"/>
+      <c r="M108" s="5"/>
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
       <c r="P108" s="1"/>
@@ -4847,26 +4875,22 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row r="109" spans="1:26" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B109" s="19"/>
-      <c r="C109" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D109" s="17"/>
-      <c r="E109" s="59"/>
-      <c r="F109" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="G109" s="60"/>
-      <c r="H109" s="39"/>
-      <c r="I109" s="18"/>
-      <c r="J109" s="1"/>
-      <c r="K109" s="1"/>
-      <c r="L109" s="1"/>
-      <c r="M109" s="1"/>
+    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A109" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="B109" s="40"/>
+      <c r="C109" s="41"/>
+      <c r="D109" s="37"/>
+      <c r="E109" s="38"/>
+      <c r="F109" s="65"/>
+      <c r="G109" s="41"/>
+      <c r="H109" s="65"/>
+      <c r="I109" s="41"/>
+      <c r="J109" s="5"/>
+      <c r="K109" s="5"/>
+      <c r="L109" s="5"/>
+      <c r="M109" s="5"/>
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
       <c r="P109" s="1"/>
@@ -4881,28 +4905,26 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
     </row>
-    <row r="110" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="B110" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C110" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="D110" s="39"/>
-      <c r="E110" s="17"/>
-      <c r="F110" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="G110" s="39"/>
-      <c r="H110" s="46"/>
-      <c r="I110" s="39"/>
-      <c r="J110" s="1"/>
-      <c r="K110" s="1"/>
-      <c r="L110" s="1"/>
-      <c r="M110" s="1"/>
+    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A110" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B110" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C110" s="41"/>
+      <c r="D110" s="37"/>
+      <c r="E110" s="38"/>
+      <c r="F110" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="G110" s="40"/>
+      <c r="H110" s="40"/>
+      <c r="I110" s="41"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="5"/>
+      <c r="M110" s="5"/>
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
       <c r="P110" s="1"/>
@@ -4917,22 +4939,26 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="B111" s="38"/>
-      <c r="C111" s="38"/>
-      <c r="D111" s="38"/>
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A111" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B111" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="C111" s="41"/>
+      <c r="D111" s="37"/>
       <c r="E111" s="38"/>
-      <c r="F111" s="38"/>
-      <c r="G111" s="38"/>
-      <c r="H111" s="38"/>
-      <c r="I111" s="39"/>
-      <c r="J111" s="1"/>
-      <c r="K111" s="1"/>
-      <c r="L111" s="1"/>
-      <c r="M111" s="1"/>
+      <c r="F111" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="G111" s="40"/>
+      <c r="H111" s="40"/>
+      <c r="I111" s="41"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="5"/>
+      <c r="M111" s="5"/>
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
       <c r="P111" s="1"/>
@@ -4947,24 +4973,26 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row r="112" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="48" t="s">
-        <v>123</v>
-      </c>
-      <c r="B112" s="38"/>
-      <c r="C112" s="39"/>
-      <c r="D112" s="49"/>
-      <c r="E112" s="50"/>
-      <c r="F112" s="55" t="s">
-        <v>124</v>
-      </c>
-      <c r="G112" s="38"/>
-      <c r="H112" s="38"/>
-      <c r="I112" s="39"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="6"/>
-      <c r="L112" s="6"/>
-      <c r="M112" s="6"/>
+    <row r="112" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="62" t="s">
+        <v>133</v>
+      </c>
+      <c r="B112" s="40"/>
+      <c r="C112" s="41"/>
+      <c r="D112" s="37"/>
+      <c r="E112" s="38"/>
+      <c r="F112" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G112" s="69" t="s">
+        <v>135</v>
+      </c>
+      <c r="H112" s="40"/>
+      <c r="I112" s="41"/>
+      <c r="J112" s="5"/>
+      <c r="K112" s="5"/>
+      <c r="L112" s="5"/>
+      <c r="M112" s="5"/>
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
       <c r="P112" s="1"/>
@@ -4980,33 +5008,29 @@
       <c r="Z112" s="1"/>
     </row>
     <row r="113" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A113" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B113" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C113" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D113" s="51"/>
-      <c r="E113" s="52"/>
-      <c r="F113" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="G113" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="H113" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="I113" s="15" t="s">
+      <c r="A113" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B113" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C113" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6"/>
-      <c r="L113" s="6"/>
-      <c r="M113" s="6"/>
+      <c r="D113" s="37"/>
+      <c r="E113" s="38"/>
+      <c r="F113" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G113" s="69" t="s">
+        <v>136</v>
+      </c>
+      <c r="H113" s="40"/>
+      <c r="I113" s="41"/>
+      <c r="J113" s="5"/>
+      <c r="K113" s="5"/>
+      <c r="L113" s="5"/>
+      <c r="M113" s="5"/>
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
       <c r="P113" s="1"/>
@@ -5022,23 +5046,25 @@
       <c r="Z113" s="1"/>
     </row>
     <row r="114" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A114" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B114" s="17"/>
-      <c r="C114" s="17"/>
-      <c r="D114" s="51"/>
-      <c r="E114" s="52"/>
-      <c r="F114" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="G114" s="17"/>
-      <c r="H114" s="17"/>
-      <c r="I114" s="17"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="6"/>
-      <c r="L114" s="6"/>
-      <c r="M114" s="6"/>
+      <c r="A114" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B114" s="16"/>
+      <c r="C114" s="16"/>
+      <c r="D114" s="37"/>
+      <c r="E114" s="38"/>
+      <c r="F114" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G114" s="69" t="s">
+        <v>137</v>
+      </c>
+      <c r="H114" s="40"/>
+      <c r="I114" s="41"/>
+      <c r="J114" s="5"/>
+      <c r="K114" s="5"/>
+      <c r="L114" s="5"/>
+      <c r="M114" s="5"/>
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
       <c r="P114" s="1"/>
@@ -5054,23 +5080,25 @@
       <c r="Z114" s="1"/>
     </row>
     <row r="115" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A115" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B115" s="17"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="51"/>
-      <c r="E115" s="52"/>
-      <c r="F115" s="42" t="s">
+      <c r="A115" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B115" s="16"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="37"/>
+      <c r="E115" s="38"/>
+      <c r="F115" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="G115" s="38"/>
-      <c r="H115" s="38"/>
-      <c r="I115" s="39"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="6"/>
-      <c r="L115" s="6"/>
-      <c r="M115" s="6"/>
+      <c r="G115" s="69" t="s">
+        <v>138</v>
+      </c>
+      <c r="H115" s="40"/>
+      <c r="I115" s="41"/>
+      <c r="J115" s="5"/>
+      <c r="K115" s="5"/>
+      <c r="L115" s="5"/>
+      <c r="M115" s="5"/>
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
       <c r="P115" s="1"/>
@@ -5086,25 +5114,25 @@
       <c r="Z115" s="1"/>
     </row>
     <row r="116" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A116" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="B116" s="39"/>
-      <c r="C116" s="22"/>
-      <c r="D116" s="51"/>
-      <c r="E116" s="52"/>
-      <c r="F116" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="G116" s="39"/>
-      <c r="H116" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="I116" s="39"/>
-      <c r="J116" s="6"/>
-      <c r="K116" s="6"/>
-      <c r="L116" s="6"/>
-      <c r="M116" s="6"/>
+      <c r="A116" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="B116" s="41"/>
+      <c r="C116" s="21"/>
+      <c r="D116" s="37"/>
+      <c r="E116" s="38"/>
+      <c r="F116" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G116" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="H116" s="40"/>
+      <c r="I116" s="41"/>
+      <c r="J116" s="5"/>
+      <c r="K116" s="5"/>
+      <c r="L116" s="5"/>
+      <c r="M116" s="5"/>
       <c r="N116" s="1"/>
       <c r="O116" s="1"/>
       <c r="P116" s="1"/>
@@ -5120,21 +5148,25 @@
       <c r="Z116" s="1"/>
     </row>
     <row r="117" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A117" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="B117" s="38"/>
-      <c r="C117" s="39"/>
-      <c r="D117" s="51"/>
-      <c r="E117" s="52"/>
-      <c r="F117" s="46"/>
-      <c r="G117" s="39"/>
-      <c r="H117" s="46"/>
-      <c r="I117" s="39"/>
-      <c r="J117" s="6"/>
-      <c r="K117" s="6"/>
-      <c r="L117" s="6"/>
-      <c r="M117" s="6"/>
+      <c r="A117" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="B117" s="40"/>
+      <c r="C117" s="41"/>
+      <c r="D117" s="37"/>
+      <c r="E117" s="38"/>
+      <c r="F117" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G117" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="H117" s="40"/>
+      <c r="I117" s="41"/>
+      <c r="J117" s="5"/>
+      <c r="K117" s="5"/>
+      <c r="L117" s="5"/>
+      <c r="M117" s="5"/>
       <c r="N117" s="1"/>
       <c r="O117" s="1"/>
       <c r="P117" s="1"/>
@@ -5150,25 +5182,27 @@
       <c r="Z117" s="1"/>
     </row>
     <row r="118" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A118" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="B118" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="C118" s="39"/>
-      <c r="D118" s="51"/>
-      <c r="E118" s="52"/>
-      <c r="F118" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="G118" s="38"/>
-      <c r="H118" s="38"/>
-      <c r="I118" s="39"/>
-      <c r="J118" s="6"/>
-      <c r="K118" s="6"/>
-      <c r="L118" s="6"/>
-      <c r="M118" s="6"/>
+      <c r="A118" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B118" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C118" s="41"/>
+      <c r="D118" s="37"/>
+      <c r="E118" s="38"/>
+      <c r="F118" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G118" s="69" t="s">
+        <v>141</v>
+      </c>
+      <c r="H118" s="40"/>
+      <c r="I118" s="41"/>
+      <c r="J118" s="5"/>
+      <c r="K118" s="5"/>
+      <c r="L118" s="5"/>
+      <c r="M118" s="5"/>
       <c r="N118" s="1"/>
       <c r="O118" s="1"/>
       <c r="P118" s="1"/>
@@ -5184,25 +5218,27 @@
       <c r="Z118" s="1"/>
     </row>
     <row r="119" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A119" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B119" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="C119" s="39"/>
-      <c r="D119" s="51"/>
-      <c r="E119" s="52"/>
-      <c r="F119" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="G119" s="38"/>
-      <c r="H119" s="38"/>
-      <c r="I119" s="39"/>
-      <c r="J119" s="6"/>
-      <c r="K119" s="6"/>
-      <c r="L119" s="6"/>
-      <c r="M119" s="6"/>
+      <c r="A119" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B119" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="C119" s="41"/>
+      <c r="D119" s="34"/>
+      <c r="E119" s="36"/>
+      <c r="F119" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G119" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="H119" s="40"/>
+      <c r="I119" s="41"/>
+      <c r="J119" s="5"/>
+      <c r="K119" s="5"/>
+      <c r="L119" s="5"/>
+      <c r="M119" s="5"/>
       <c r="N119" s="1"/>
       <c r="O119" s="1"/>
       <c r="P119" s="1"/>
@@ -5217,26 +5253,20 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
     </row>
-    <row r="120" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="B120" s="38"/>
-      <c r="C120" s="39"/>
-      <c r="D120" s="51"/>
-      <c r="E120" s="52"/>
-      <c r="F120" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G120" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="H120" s="38"/>
-      <c r="I120" s="39"/>
-      <c r="J120" s="6"/>
-      <c r="K120" s="6"/>
-      <c r="L120" s="6"/>
-      <c r="M120" s="6"/>
+    <row r="120" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="95"/>
+      <c r="B120" s="96"/>
+      <c r="C120" s="95"/>
+      <c r="D120" s="96"/>
+      <c r="E120" s="95"/>
+      <c r="F120" s="97"/>
+      <c r="G120" s="96"/>
+      <c r="H120" s="95"/>
+      <c r="I120" s="96"/>
+      <c r="J120" s="1"/>
+      <c r="K120" s="5"/>
+      <c r="L120" s="5"/>
+      <c r="M120" s="1"/>
       <c r="N120" s="1"/>
       <c r="O120" s="1"/>
       <c r="P120" s="1"/>
@@ -5251,30 +5281,20 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A121" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B121" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C121" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D121" s="51"/>
-      <c r="E121" s="52"/>
-      <c r="F121" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G121" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="H121" s="38"/>
-      <c r="I121" s="39"/>
-      <c r="J121" s="6"/>
-      <c r="K121" s="6"/>
-      <c r="L121" s="6"/>
-      <c r="M121" s="6"/>
+    <row r="121" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="98"/>
+      <c r="B121" s="99"/>
+      <c r="C121" s="98"/>
+      <c r="D121" s="99"/>
+      <c r="E121" s="98"/>
+      <c r="F121" s="100"/>
+      <c r="G121" s="99"/>
+      <c r="H121" s="98"/>
+      <c r="I121" s="99"/>
+      <c r="J121" s="1"/>
+      <c r="K121" s="5"/>
+      <c r="L121" s="5"/>
+      <c r="M121" s="1"/>
       <c r="N121" s="1"/>
       <c r="O121" s="1"/>
       <c r="P121" s="1"/>
@@ -5289,26 +5309,20 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A122" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B122" s="17"/>
-      <c r="C122" s="17"/>
-      <c r="D122" s="51"/>
-      <c r="E122" s="52"/>
-      <c r="F122" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G122" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="H122" s="38"/>
-      <c r="I122" s="39"/>
-      <c r="J122" s="6"/>
-      <c r="K122" s="6"/>
-      <c r="L122" s="6"/>
-      <c r="M122" s="6"/>
+    <row r="122" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="98"/>
+      <c r="B122" s="99"/>
+      <c r="C122" s="98"/>
+      <c r="D122" s="99"/>
+      <c r="E122" s="98"/>
+      <c r="F122" s="100"/>
+      <c r="G122" s="99"/>
+      <c r="H122" s="98"/>
+      <c r="I122" s="99"/>
+      <c r="J122" s="1"/>
+      <c r="K122" s="5"/>
+      <c r="L122" s="5"/>
+      <c r="M122" s="1"/>
       <c r="N122" s="1"/>
       <c r="O122" s="1"/>
       <c r="P122" s="1"/>
@@ -5323,26 +5337,20 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A123" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B123" s="17"/>
-      <c r="C123" s="17"/>
-      <c r="D123" s="51"/>
-      <c r="E123" s="52"/>
-      <c r="F123" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G123" s="45" t="s">
-        <v>147</v>
-      </c>
-      <c r="H123" s="38"/>
-      <c r="I123" s="39"/>
-      <c r="J123" s="6"/>
-      <c r="K123" s="6"/>
-      <c r="L123" s="6"/>
-      <c r="M123" s="6"/>
+    <row r="123" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="98"/>
+      <c r="B123" s="99"/>
+      <c r="C123" s="98"/>
+      <c r="D123" s="99"/>
+      <c r="E123" s="98"/>
+      <c r="F123" s="100"/>
+      <c r="G123" s="99"/>
+      <c r="H123" s="98"/>
+      <c r="I123" s="99"/>
+      <c r="J123" s="1"/>
+      <c r="K123" s="5"/>
+      <c r="L123" s="5"/>
+      <c r="M123" s="1"/>
       <c r="N123" s="1"/>
       <c r="O123" s="1"/>
       <c r="P123" s="1"/>
@@ -5357,26 +5365,20 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A124" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="B124" s="39"/>
-      <c r="C124" s="22"/>
-      <c r="D124" s="51"/>
-      <c r="E124" s="52"/>
-      <c r="F124" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G124" s="45" t="s">
-        <v>148</v>
-      </c>
-      <c r="H124" s="38"/>
-      <c r="I124" s="39"/>
-      <c r="J124" s="6"/>
-      <c r="K124" s="6"/>
-      <c r="L124" s="6"/>
-      <c r="M124" s="6"/>
+    <row r="124" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="98"/>
+      <c r="B124" s="99"/>
+      <c r="C124" s="98"/>
+      <c r="D124" s="99"/>
+      <c r="E124" s="98"/>
+      <c r="F124" s="100"/>
+      <c r="G124" s="99"/>
+      <c r="H124" s="98"/>
+      <c r="I124" s="99"/>
+      <c r="J124" s="1"/>
+      <c r="K124" s="5"/>
+      <c r="L124" s="5"/>
+      <c r="M124" s="1"/>
       <c r="N124" s="1"/>
       <c r="O124" s="1"/>
       <c r="P124" s="1"/>
@@ -5391,26 +5393,20 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
     </row>
-    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A125" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="B125" s="38"/>
-      <c r="C125" s="39"/>
-      <c r="D125" s="51"/>
-      <c r="E125" s="52"/>
-      <c r="F125" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G125" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="H125" s="38"/>
-      <c r="I125" s="39"/>
-      <c r="J125" s="6"/>
-      <c r="K125" s="6"/>
-      <c r="L125" s="6"/>
-      <c r="M125" s="6"/>
+    <row r="125" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="98"/>
+      <c r="B125" s="99"/>
+      <c r="C125" s="98"/>
+      <c r="D125" s="99"/>
+      <c r="E125" s="98"/>
+      <c r="F125" s="100"/>
+      <c r="G125" s="99"/>
+      <c r="H125" s="98"/>
+      <c r="I125" s="99"/>
+      <c r="J125" s="1"/>
+      <c r="K125" s="5"/>
+      <c r="L125" s="5"/>
+      <c r="M125" s="1"/>
       <c r="N125" s="1"/>
       <c r="O125" s="1"/>
       <c r="P125" s="1"/>
@@ -5425,28 +5421,20 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A126" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="B126" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="C126" s="39"/>
-      <c r="D126" s="51"/>
-      <c r="E126" s="52"/>
-      <c r="F126" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G126" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="H126" s="38"/>
-      <c r="I126" s="39"/>
-      <c r="J126" s="6"/>
-      <c r="K126" s="6"/>
-      <c r="L126" s="6"/>
-      <c r="M126" s="6"/>
+    <row r="126" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="98"/>
+      <c r="B126" s="99"/>
+      <c r="C126" s="98"/>
+      <c r="D126" s="99"/>
+      <c r="E126" s="98"/>
+      <c r="F126" s="100"/>
+      <c r="G126" s="99"/>
+      <c r="H126" s="98"/>
+      <c r="I126" s="99"/>
+      <c r="J126" s="1"/>
+      <c r="K126" s="5"/>
+      <c r="L126" s="5"/>
+      <c r="M126" s="1"/>
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
       <c r="P126" s="1"/>
@@ -5461,28 +5449,20 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A127" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B127" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="C127" s="39"/>
-      <c r="D127" s="53"/>
-      <c r="E127" s="54"/>
-      <c r="F127" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G127" s="45" t="s">
-        <v>151</v>
-      </c>
-      <c r="H127" s="38"/>
-      <c r="I127" s="39"/>
-      <c r="J127" s="6"/>
-      <c r="K127" s="6"/>
-      <c r="L127" s="6"/>
-      <c r="M127" s="6"/>
+    <row r="127" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="98"/>
+      <c r="B127" s="99"/>
+      <c r="C127" s="98"/>
+      <c r="D127" s="99"/>
+      <c r="E127" s="98"/>
+      <c r="F127" s="100"/>
+      <c r="G127" s="99"/>
+      <c r="H127" s="98"/>
+      <c r="I127" s="99"/>
+      <c r="J127" s="1"/>
+      <c r="K127" s="5"/>
+      <c r="L127" s="5"/>
+      <c r="M127" s="1"/>
       <c r="N127" s="1"/>
       <c r="O127" s="1"/>
       <c r="P127" s="1"/>
@@ -5498,18 +5478,18 @@
       <c r="Z127" s="1"/>
     </row>
     <row r="128" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="32"/>
-      <c r="B128" s="27"/>
-      <c r="C128" s="32"/>
-      <c r="D128" s="27"/>
-      <c r="E128" s="32"/>
-      <c r="F128" s="33"/>
-      <c r="G128" s="27"/>
-      <c r="H128" s="32"/>
-      <c r="I128" s="27"/>
+      <c r="A128" s="98"/>
+      <c r="B128" s="99"/>
+      <c r="C128" s="98"/>
+      <c r="D128" s="99"/>
+      <c r="E128" s="98"/>
+      <c r="F128" s="100"/>
+      <c r="G128" s="99"/>
+      <c r="H128" s="98"/>
+      <c r="I128" s="99"/>
       <c r="J128" s="1"/>
-      <c r="K128" s="6"/>
-      <c r="L128" s="6"/>
+      <c r="K128" s="5"/>
+      <c r="L128" s="5"/>
       <c r="M128" s="1"/>
       <c r="N128" s="1"/>
       <c r="O128" s="1"/>
@@ -5526,18 +5506,18 @@
       <c r="Z128" s="1"/>
     </row>
     <row r="129" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="28"/>
-      <c r="B129" s="29"/>
-      <c r="C129" s="28"/>
-      <c r="D129" s="29"/>
-      <c r="E129" s="28"/>
-      <c r="F129" s="34"/>
-      <c r="G129" s="29"/>
-      <c r="H129" s="28"/>
-      <c r="I129" s="29"/>
+      <c r="A129" s="98"/>
+      <c r="B129" s="99"/>
+      <c r="C129" s="98"/>
+      <c r="D129" s="99"/>
+      <c r="E129" s="98"/>
+      <c r="F129" s="100"/>
+      <c r="G129" s="99"/>
+      <c r="H129" s="98"/>
+      <c r="I129" s="99"/>
       <c r="J129" s="1"/>
-      <c r="K129" s="6"/>
-      <c r="L129" s="6"/>
+      <c r="K129" s="5"/>
+      <c r="L129" s="5"/>
       <c r="M129" s="1"/>
       <c r="N129" s="1"/>
       <c r="O129" s="1"/>
@@ -5554,18 +5534,18 @@
       <c r="Z129" s="1"/>
     </row>
     <row r="130" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="28"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="28"/>
-      <c r="D130" s="29"/>
-      <c r="E130" s="28"/>
-      <c r="F130" s="34"/>
-      <c r="G130" s="29"/>
-      <c r="H130" s="28"/>
-      <c r="I130" s="29"/>
+      <c r="A130" s="98"/>
+      <c r="B130" s="99"/>
+      <c r="C130" s="98"/>
+      <c r="D130" s="99"/>
+      <c r="E130" s="98"/>
+      <c r="F130" s="100"/>
+      <c r="G130" s="99"/>
+      <c r="H130" s="98"/>
+      <c r="I130" s="99"/>
       <c r="J130" s="1"/>
-      <c r="K130" s="6"/>
-      <c r="L130" s="6"/>
+      <c r="K130" s="5"/>
+      <c r="L130" s="5"/>
       <c r="M130" s="1"/>
       <c r="N130" s="1"/>
       <c r="O130" s="1"/>
@@ -5582,18 +5562,18 @@
       <c r="Z130" s="1"/>
     </row>
     <row r="131" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="28"/>
-      <c r="B131" s="29"/>
-      <c r="C131" s="28"/>
-      <c r="D131" s="29"/>
-      <c r="E131" s="28"/>
-      <c r="F131" s="34"/>
-      <c r="G131" s="29"/>
-      <c r="H131" s="28"/>
-      <c r="I131" s="29"/>
+      <c r="A131" s="101"/>
+      <c r="B131" s="102"/>
+      <c r="C131" s="101"/>
+      <c r="D131" s="102"/>
+      <c r="E131" s="101"/>
+      <c r="F131" s="103"/>
+      <c r="G131" s="102"/>
+      <c r="H131" s="101"/>
+      <c r="I131" s="102"/>
       <c r="J131" s="1"/>
-      <c r="K131" s="6"/>
-      <c r="L131" s="6"/>
+      <c r="K131" s="5"/>
+      <c r="L131" s="5"/>
       <c r="M131" s="1"/>
       <c r="N131" s="1"/>
       <c r="O131" s="1"/>
@@ -5610,18 +5590,26 @@
       <c r="Z131" s="1"/>
     </row>
     <row r="132" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="28"/>
-      <c r="B132" s="29"/>
-      <c r="C132" s="28"/>
-      <c r="D132" s="29"/>
-      <c r="E132" s="28"/>
-      <c r="F132" s="34"/>
-      <c r="G132" s="29"/>
-      <c r="H132" s="28"/>
-      <c r="I132" s="29"/>
+      <c r="A132" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="B132" s="41"/>
+      <c r="C132" s="70" t="s">
+        <v>143</v>
+      </c>
+      <c r="D132" s="33"/>
+      <c r="E132" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="F132" s="40"/>
+      <c r="G132" s="41"/>
+      <c r="H132" s="70" t="s">
+        <v>145</v>
+      </c>
+      <c r="I132" s="33"/>
       <c r="J132" s="1"/>
-      <c r="K132" s="6"/>
-      <c r="L132" s="6"/>
+      <c r="K132" s="5"/>
+      <c r="L132" s="5"/>
       <c r="M132" s="1"/>
       <c r="N132" s="1"/>
       <c r="O132" s="1"/>
@@ -5638,18 +5626,18 @@
       <c r="Z132" s="1"/>
     </row>
     <row r="133" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="28"/>
-      <c r="B133" s="29"/>
-      <c r="C133" s="28"/>
-      <c r="D133" s="29"/>
-      <c r="E133" s="28"/>
-      <c r="F133" s="34"/>
-      <c r="G133" s="29"/>
-      <c r="H133" s="28"/>
-      <c r="I133" s="29"/>
+      <c r="A133" s="95"/>
+      <c r="B133" s="97"/>
+      <c r="C133" s="104"/>
+      <c r="D133" s="105"/>
+      <c r="E133" s="97"/>
+      <c r="F133" s="97"/>
+      <c r="G133" s="97"/>
+      <c r="H133" s="104"/>
+      <c r="I133" s="105"/>
       <c r="J133" s="1"/>
-      <c r="K133" s="6"/>
-      <c r="L133" s="6"/>
+      <c r="K133" s="1"/>
+      <c r="L133" s="1"/>
       <c r="M133" s="1"/>
       <c r="N133" s="1"/>
       <c r="O133" s="1"/>
@@ -5666,18 +5654,18 @@
       <c r="Z133" s="1"/>
     </row>
     <row r="134" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="28"/>
-      <c r="B134" s="29"/>
-      <c r="C134" s="28"/>
-      <c r="D134" s="29"/>
-      <c r="E134" s="28"/>
-      <c r="F134" s="34"/>
-      <c r="G134" s="29"/>
-      <c r="H134" s="28"/>
-      <c r="I134" s="29"/>
+      <c r="A134" s="98"/>
+      <c r="B134" s="100"/>
+      <c r="C134" s="106"/>
+      <c r="D134" s="107"/>
+      <c r="E134" s="100"/>
+      <c r="F134" s="100"/>
+      <c r="G134" s="100"/>
+      <c r="H134" s="106"/>
+      <c r="I134" s="108"/>
       <c r="J134" s="1"/>
-      <c r="K134" s="6"/>
-      <c r="L134" s="6"/>
+      <c r="K134" s="1"/>
+      <c r="L134" s="1"/>
       <c r="M134" s="1"/>
       <c r="N134" s="1"/>
       <c r="O134" s="1"/>
@@ -5694,18 +5682,18 @@
       <c r="Z134" s="1"/>
     </row>
     <row r="135" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="28"/>
-      <c r="B135" s="29"/>
-      <c r="C135" s="28"/>
-      <c r="D135" s="29"/>
-      <c r="E135" s="28"/>
-      <c r="F135" s="34"/>
-      <c r="G135" s="29"/>
-      <c r="H135" s="28"/>
-      <c r="I135" s="29"/>
+      <c r="A135" s="98"/>
+      <c r="B135" s="100"/>
+      <c r="C135" s="106"/>
+      <c r="D135" s="107"/>
+      <c r="E135" s="100"/>
+      <c r="F135" s="100"/>
+      <c r="G135" s="100"/>
+      <c r="H135" s="106"/>
+      <c r="I135" s="108"/>
       <c r="J135" s="1"/>
-      <c r="K135" s="6"/>
-      <c r="L135" s="6"/>
+      <c r="K135" s="1"/>
+      <c r="L135" s="1"/>
       <c r="M135" s="1"/>
       <c r="N135" s="1"/>
       <c r="O135" s="1"/>
@@ -5722,18 +5710,18 @@
       <c r="Z135" s="1"/>
     </row>
     <row r="136" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="28"/>
-      <c r="B136" s="29"/>
-      <c r="C136" s="28"/>
-      <c r="D136" s="29"/>
-      <c r="E136" s="28"/>
-      <c r="F136" s="34"/>
-      <c r="G136" s="29"/>
-      <c r="H136" s="28"/>
-      <c r="I136" s="29"/>
+      <c r="A136" s="98"/>
+      <c r="B136" s="100"/>
+      <c r="C136" s="106"/>
+      <c r="D136" s="107"/>
+      <c r="E136" s="100"/>
+      <c r="F136" s="100"/>
+      <c r="G136" s="100"/>
+      <c r="H136" s="106"/>
+      <c r="I136" s="108"/>
       <c r="J136" s="1"/>
-      <c r="K136" s="6"/>
-      <c r="L136" s="6"/>
+      <c r="K136" s="1"/>
+      <c r="L136" s="1"/>
       <c r="M136" s="1"/>
       <c r="N136" s="1"/>
       <c r="O136" s="1"/>
@@ -5750,18 +5738,18 @@
       <c r="Z136" s="1"/>
     </row>
     <row r="137" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="28"/>
-      <c r="B137" s="29"/>
-      <c r="C137" s="28"/>
-      <c r="D137" s="29"/>
-      <c r="E137" s="28"/>
-      <c r="F137" s="34"/>
-      <c r="G137" s="29"/>
-      <c r="H137" s="28"/>
-      <c r="I137" s="29"/>
+      <c r="A137" s="98"/>
+      <c r="B137" s="100"/>
+      <c r="C137" s="106"/>
+      <c r="D137" s="107"/>
+      <c r="E137" s="100"/>
+      <c r="F137" s="100"/>
+      <c r="G137" s="100"/>
+      <c r="H137" s="106"/>
+      <c r="I137" s="108"/>
       <c r="J137" s="1"/>
-      <c r="K137" s="6"/>
-      <c r="L137" s="6"/>
+      <c r="K137" s="1"/>
+      <c r="L137" s="1"/>
       <c r="M137" s="1"/>
       <c r="N137" s="1"/>
       <c r="O137" s="1"/>
@@ -5778,18 +5766,18 @@
       <c r="Z137" s="1"/>
     </row>
     <row r="138" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="28"/>
-      <c r="B138" s="29"/>
-      <c r="C138" s="28"/>
-      <c r="D138" s="29"/>
-      <c r="E138" s="28"/>
-      <c r="F138" s="34"/>
-      <c r="G138" s="29"/>
-      <c r="H138" s="28"/>
-      <c r="I138" s="29"/>
+      <c r="A138" s="98"/>
+      <c r="B138" s="100"/>
+      <c r="C138" s="106"/>
+      <c r="D138" s="107"/>
+      <c r="E138" s="100"/>
+      <c r="F138" s="100"/>
+      <c r="G138" s="100"/>
+      <c r="H138" s="106"/>
+      <c r="I138" s="108"/>
       <c r="J138" s="1"/>
-      <c r="K138" s="6"/>
-      <c r="L138" s="6"/>
+      <c r="K138" s="1"/>
+      <c r="L138" s="1"/>
       <c r="M138" s="1"/>
       <c r="N138" s="1"/>
       <c r="O138" s="1"/>
@@ -5806,18 +5794,18 @@
       <c r="Z138" s="1"/>
     </row>
     <row r="139" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="30"/>
-      <c r="B139" s="31"/>
-      <c r="C139" s="30"/>
-      <c r="D139" s="31"/>
-      <c r="E139" s="30"/>
-      <c r="F139" s="35"/>
-      <c r="G139" s="31"/>
-      <c r="H139" s="30"/>
-      <c r="I139" s="31"/>
+      <c r="A139" s="98"/>
+      <c r="B139" s="100"/>
+      <c r="C139" s="106"/>
+      <c r="D139" s="107"/>
+      <c r="E139" s="100"/>
+      <c r="F139" s="100"/>
+      <c r="G139" s="100"/>
+      <c r="H139" s="106"/>
+      <c r="I139" s="108"/>
       <c r="J139" s="1"/>
-      <c r="K139" s="6"/>
-      <c r="L139" s="6"/>
+      <c r="K139" s="1"/>
+      <c r="L139" s="1"/>
       <c r="M139" s="1"/>
       <c r="N139" s="1"/>
       <c r="O139" s="1"/>
@@ -5834,26 +5822,18 @@
       <c r="Z139" s="1"/>
     </row>
     <row r="140" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="B140" s="39"/>
-      <c r="C140" s="83" t="s">
-        <v>152</v>
-      </c>
-      <c r="D140" s="50"/>
-      <c r="E140" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="F140" s="38"/>
-      <c r="G140" s="39"/>
-      <c r="H140" s="83" t="s">
-        <v>154</v>
-      </c>
-      <c r="I140" s="50"/>
+      <c r="A140" s="98"/>
+      <c r="B140" s="100"/>
+      <c r="C140" s="106"/>
+      <c r="D140" s="107"/>
+      <c r="E140" s="100"/>
+      <c r="F140" s="100"/>
+      <c r="G140" s="100"/>
+      <c r="H140" s="106"/>
+      <c r="I140" s="108"/>
       <c r="J140" s="1"/>
-      <c r="K140" s="6"/>
-      <c r="L140" s="6"/>
+      <c r="K140" s="1"/>
+      <c r="L140" s="1"/>
       <c r="M140" s="1"/>
       <c r="N140" s="1"/>
       <c r="O140" s="1"/>
@@ -5870,15 +5850,15 @@
       <c r="Z140" s="1"/>
     </row>
     <row r="141" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="32"/>
-      <c r="B141" s="33"/>
-      <c r="C141" s="85"/>
-      <c r="D141" s="86"/>
-      <c r="E141" s="33"/>
-      <c r="F141" s="33"/>
-      <c r="G141" s="33"/>
-      <c r="H141" s="85"/>
-      <c r="I141" s="86"/>
+      <c r="A141" s="98"/>
+      <c r="B141" s="100"/>
+      <c r="C141" s="106"/>
+      <c r="D141" s="107"/>
+      <c r="E141" s="100"/>
+      <c r="F141" s="100"/>
+      <c r="G141" s="100"/>
+      <c r="H141" s="106"/>
+      <c r="I141" s="108"/>
       <c r="J141" s="1"/>
       <c r="K141" s="1"/>
       <c r="L141" s="1"/>
@@ -5898,23 +5878,23 @@
       <c r="Z141" s="1"/>
     </row>
     <row r="142" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="28"/>
-      <c r="B142" s="34"/>
-      <c r="C142" s="87"/>
-      <c r="D142" s="88"/>
-      <c r="E142" s="34"/>
-      <c r="F142" s="34"/>
-      <c r="G142" s="34"/>
-      <c r="H142" s="87"/>
-      <c r="I142" s="91"/>
-      <c r="J142" s="1"/>
-      <c r="K142" s="1"/>
-      <c r="L142" s="1"/>
-      <c r="M142" s="1"/>
-      <c r="N142" s="1"/>
-      <c r="O142" s="1"/>
-      <c r="P142" s="1"/>
-      <c r="Q142" s="1"/>
+      <c r="A142" s="98"/>
+      <c r="B142" s="100"/>
+      <c r="C142" s="106"/>
+      <c r="D142" s="107"/>
+      <c r="E142" s="100"/>
+      <c r="F142" s="100"/>
+      <c r="G142" s="100"/>
+      <c r="H142" s="106"/>
+      <c r="I142" s="108"/>
+      <c r="J142" s="22"/>
+      <c r="K142" s="22"/>
+      <c r="L142" s="22"/>
+      <c r="M142" s="22"/>
+      <c r="N142" s="22"/>
+      <c r="O142" s="22"/>
+      <c r="P142" s="22"/>
+      <c r="Q142" s="22"/>
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
       <c r="T142" s="1"/>
@@ -5926,23 +5906,23 @@
       <c r="Z142" s="1"/>
     </row>
     <row r="143" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="28"/>
-      <c r="B143" s="34"/>
-      <c r="C143" s="87"/>
-      <c r="D143" s="88"/>
-      <c r="E143" s="34"/>
-      <c r="F143" s="34"/>
-      <c r="G143" s="34"/>
-      <c r="H143" s="87"/>
-      <c r="I143" s="91"/>
-      <c r="J143" s="1"/>
-      <c r="K143" s="1"/>
-      <c r="L143" s="1"/>
-      <c r="M143" s="1"/>
-      <c r="N143" s="1"/>
-      <c r="O143" s="1"/>
-      <c r="P143" s="1"/>
-      <c r="Q143" s="1"/>
+      <c r="A143" s="98"/>
+      <c r="B143" s="100"/>
+      <c r="C143" s="106"/>
+      <c r="D143" s="107"/>
+      <c r="E143" s="100"/>
+      <c r="F143" s="100"/>
+      <c r="G143" s="100"/>
+      <c r="H143" s="106"/>
+      <c r="I143" s="108"/>
+      <c r="J143" s="22"/>
+      <c r="K143" s="22"/>
+      <c r="L143" s="22"/>
+      <c r="M143" s="22"/>
+      <c r="N143" s="22"/>
+      <c r="O143" s="22"/>
+      <c r="P143" s="22"/>
+      <c r="Q143" s="22"/>
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
       <c r="T143" s="1"/>
@@ -5954,23 +5934,23 @@
       <c r="Z143" s="1"/>
     </row>
     <row r="144" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="28"/>
-      <c r="B144" s="34"/>
-      <c r="C144" s="87"/>
-      <c r="D144" s="88"/>
-      <c r="E144" s="34"/>
-      <c r="F144" s="34"/>
-      <c r="G144" s="34"/>
-      <c r="H144" s="87"/>
-      <c r="I144" s="91"/>
-      <c r="J144" s="1"/>
-      <c r="K144" s="1"/>
-      <c r="L144" s="1"/>
-      <c r="M144" s="1"/>
-      <c r="N144" s="1"/>
-      <c r="O144" s="1"/>
-      <c r="P144" s="1"/>
-      <c r="Q144" s="1"/>
+      <c r="A144" s="98"/>
+      <c r="B144" s="100"/>
+      <c r="C144" s="106"/>
+      <c r="D144" s="107"/>
+      <c r="E144" s="100"/>
+      <c r="F144" s="100"/>
+      <c r="G144" s="100"/>
+      <c r="H144" s="106"/>
+      <c r="I144" s="108"/>
+      <c r="J144" s="22"/>
+      <c r="K144" s="22"/>
+      <c r="L144" s="22"/>
+      <c r="M144" s="22"/>
+      <c r="N144" s="22"/>
+      <c r="O144" s="22"/>
+      <c r="P144" s="22"/>
+      <c r="Q144" s="22"/>
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
       <c r="T144" s="1"/>
@@ -5982,23 +5962,23 @@
       <c r="Z144" s="1"/>
     </row>
     <row r="145" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="28"/>
-      <c r="B145" s="34"/>
-      <c r="C145" s="87"/>
-      <c r="D145" s="88"/>
-      <c r="E145" s="34"/>
-      <c r="F145" s="34"/>
-      <c r="G145" s="34"/>
-      <c r="H145" s="87"/>
-      <c r="I145" s="91"/>
-      <c r="J145" s="1"/>
-      <c r="K145" s="1"/>
-      <c r="L145" s="1"/>
-      <c r="M145" s="1"/>
-      <c r="N145" s="1"/>
-      <c r="O145" s="1"/>
-      <c r="P145" s="1"/>
-      <c r="Q145" s="1"/>
+      <c r="A145" s="98"/>
+      <c r="B145" s="100"/>
+      <c r="C145" s="106"/>
+      <c r="D145" s="107"/>
+      <c r="E145" s="100"/>
+      <c r="F145" s="100"/>
+      <c r="G145" s="100"/>
+      <c r="H145" s="106"/>
+      <c r="I145" s="108"/>
+      <c r="J145" s="22"/>
+      <c r="K145" s="22"/>
+      <c r="L145" s="22"/>
+      <c r="M145" s="22"/>
+      <c r="N145" s="22"/>
+      <c r="O145" s="22"/>
+      <c r="P145" s="22"/>
+      <c r="Q145" s="22"/>
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
@@ -6010,23 +5990,23 @@
       <c r="Z145" s="1"/>
     </row>
     <row r="146" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="28"/>
-      <c r="B146" s="34"/>
-      <c r="C146" s="87"/>
-      <c r="D146" s="88"/>
-      <c r="E146" s="34"/>
-      <c r="F146" s="34"/>
-      <c r="G146" s="34"/>
-      <c r="H146" s="87"/>
-      <c r="I146" s="91"/>
-      <c r="J146" s="1"/>
-      <c r="K146" s="1"/>
-      <c r="L146" s="1"/>
-      <c r="M146" s="1"/>
-      <c r="N146" s="1"/>
-      <c r="O146" s="1"/>
-      <c r="P146" s="1"/>
-      <c r="Q146" s="1"/>
+      <c r="A146" s="101"/>
+      <c r="B146" s="103"/>
+      <c r="C146" s="109"/>
+      <c r="D146" s="110"/>
+      <c r="E146" s="103"/>
+      <c r="F146" s="103"/>
+      <c r="G146" s="103"/>
+      <c r="H146" s="109"/>
+      <c r="I146" s="110"/>
+      <c r="J146" s="22"/>
+      <c r="K146" s="22"/>
+      <c r="L146" s="22"/>
+      <c r="M146" s="22"/>
+      <c r="N146" s="22"/>
+      <c r="O146" s="22"/>
+      <c r="P146" s="22"/>
+      <c r="Q146" s="22"/>
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
       <c r="T146" s="1"/>
@@ -6038,23 +6018,31 @@
       <c r="Z146" s="1"/>
     </row>
     <row r="147" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="28"/>
-      <c r="B147" s="34"/>
-      <c r="C147" s="87"/>
-      <c r="D147" s="88"/>
-      <c r="E147" s="34"/>
-      <c r="F147" s="34"/>
-      <c r="G147" s="34"/>
-      <c r="H147" s="87"/>
-      <c r="I147" s="91"/>
-      <c r="J147" s="1"/>
-      <c r="K147" s="1"/>
-      <c r="L147" s="1"/>
-      <c r="M147" s="1"/>
-      <c r="N147" s="1"/>
-      <c r="O147" s="1"/>
-      <c r="P147" s="1"/>
-      <c r="Q147" s="1"/>
+      <c r="A147" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="B147" s="41"/>
+      <c r="C147" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="D147" s="36"/>
+      <c r="E147" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F147" s="40"/>
+      <c r="G147" s="41"/>
+      <c r="H147" s="71" t="s">
+        <v>149</v>
+      </c>
+      <c r="I147" s="36"/>
+      <c r="J147" s="22"/>
+      <c r="K147" s="22"/>
+      <c r="L147" s="22"/>
+      <c r="M147" s="22"/>
+      <c r="N147" s="22"/>
+      <c r="O147" s="22"/>
+      <c r="P147" s="22"/>
+      <c r="Q147" s="22"/>
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
       <c r="T147" s="1"/>
@@ -6066,23 +6054,23 @@
       <c r="Z147" s="1"/>
     </row>
     <row r="148" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="28"/>
-      <c r="B148" s="34"/>
-      <c r="C148" s="87"/>
-      <c r="D148" s="88"/>
-      <c r="E148" s="34"/>
-      <c r="F148" s="34"/>
-      <c r="G148" s="34"/>
-      <c r="H148" s="87"/>
-      <c r="I148" s="91"/>
-      <c r="J148" s="1"/>
-      <c r="K148" s="1"/>
-      <c r="L148" s="1"/>
-      <c r="M148" s="1"/>
-      <c r="N148" s="1"/>
-      <c r="O148" s="1"/>
-      <c r="P148" s="1"/>
-      <c r="Q148" s="1"/>
+      <c r="A148" s="111"/>
+      <c r="B148" s="96"/>
+      <c r="C148" s="111"/>
+      <c r="D148" s="96"/>
+      <c r="E148" s="111"/>
+      <c r="F148" s="97"/>
+      <c r="G148" s="96"/>
+      <c r="H148" s="111"/>
+      <c r="I148" s="96"/>
+      <c r="J148" s="22"/>
+      <c r="K148" s="22"/>
+      <c r="L148" s="22"/>
+      <c r="M148" s="22"/>
+      <c r="N148" s="22"/>
+      <c r="O148" s="22"/>
+      <c r="P148" s="22"/>
+      <c r="Q148" s="22"/>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
       <c r="T148" s="1"/>
@@ -6094,23 +6082,23 @@
       <c r="Z148" s="1"/>
     </row>
     <row r="149" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="28"/>
-      <c r="B149" s="34"/>
-      <c r="C149" s="87"/>
-      <c r="D149" s="88"/>
-      <c r="E149" s="34"/>
-      <c r="F149" s="34"/>
-      <c r="G149" s="34"/>
-      <c r="H149" s="87"/>
-      <c r="I149" s="91"/>
-      <c r="J149" s="1"/>
-      <c r="K149" s="1"/>
-      <c r="L149" s="1"/>
-      <c r="M149" s="1"/>
-      <c r="N149" s="1"/>
-      <c r="O149" s="1"/>
-      <c r="P149" s="1"/>
-      <c r="Q149" s="1"/>
+      <c r="A149" s="98"/>
+      <c r="B149" s="99"/>
+      <c r="C149" s="98"/>
+      <c r="D149" s="99"/>
+      <c r="E149" s="98"/>
+      <c r="F149" s="100"/>
+      <c r="G149" s="99"/>
+      <c r="H149" s="98"/>
+      <c r="I149" s="99"/>
+      <c r="J149" s="22"/>
+      <c r="K149" s="22"/>
+      <c r="L149" s="22"/>
+      <c r="M149" s="22"/>
+      <c r="N149" s="22"/>
+      <c r="O149" s="22"/>
+      <c r="P149" s="22"/>
+      <c r="Q149" s="22"/>
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
       <c r="T149" s="1"/>
@@ -6122,23 +6110,23 @@
       <c r="Z149" s="1"/>
     </row>
     <row r="150" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="28"/>
-      <c r="B150" s="34"/>
-      <c r="C150" s="87"/>
-      <c r="D150" s="88"/>
-      <c r="E150" s="34"/>
-      <c r="F150" s="34"/>
-      <c r="G150" s="34"/>
-      <c r="H150" s="87"/>
-      <c r="I150" s="91"/>
-      <c r="J150" s="23"/>
-      <c r="K150" s="23"/>
-      <c r="L150" s="23"/>
-      <c r="M150" s="23"/>
-      <c r="N150" s="23"/>
-      <c r="O150" s="23"/>
-      <c r="P150" s="23"/>
-      <c r="Q150" s="23"/>
+      <c r="A150" s="98"/>
+      <c r="B150" s="99"/>
+      <c r="C150" s="98"/>
+      <c r="D150" s="99"/>
+      <c r="E150" s="98"/>
+      <c r="F150" s="100"/>
+      <c r="G150" s="99"/>
+      <c r="H150" s="98"/>
+      <c r="I150" s="99"/>
+      <c r="J150" s="22"/>
+      <c r="K150" s="22"/>
+      <c r="L150" s="22"/>
+      <c r="M150" s="22"/>
+      <c r="N150" s="22"/>
+      <c r="O150" s="22"/>
+      <c r="P150" s="22"/>
+      <c r="Q150" s="22"/>
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
       <c r="T150" s="1"/>
@@ -6150,23 +6138,23 @@
       <c r="Z150" s="1"/>
     </row>
     <row r="151" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="28"/>
-      <c r="B151" s="34"/>
-      <c r="C151" s="87"/>
-      <c r="D151" s="88"/>
-      <c r="E151" s="34"/>
-      <c r="F151" s="34"/>
-      <c r="G151" s="34"/>
-      <c r="H151" s="87"/>
-      <c r="I151" s="91"/>
-      <c r="J151" s="23"/>
-      <c r="K151" s="23"/>
-      <c r="L151" s="23"/>
-      <c r="M151" s="23"/>
-      <c r="N151" s="23"/>
-      <c r="O151" s="23"/>
-      <c r="P151" s="23"/>
-      <c r="Q151" s="23"/>
+      <c r="A151" s="98"/>
+      <c r="B151" s="99"/>
+      <c r="C151" s="98"/>
+      <c r="D151" s="99"/>
+      <c r="E151" s="98"/>
+      <c r="F151" s="100"/>
+      <c r="G151" s="99"/>
+      <c r="H151" s="98"/>
+      <c r="I151" s="99"/>
+      <c r="J151" s="22"/>
+      <c r="K151" s="22"/>
+      <c r="L151" s="22"/>
+      <c r="M151" s="22"/>
+      <c r="N151" s="22"/>
+      <c r="O151" s="22"/>
+      <c r="P151" s="22"/>
+      <c r="Q151" s="22"/>
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
       <c r="T151" s="1"/>
@@ -6178,23 +6166,23 @@
       <c r="Z151" s="1"/>
     </row>
     <row r="152" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="28"/>
-      <c r="B152" s="34"/>
-      <c r="C152" s="87"/>
-      <c r="D152" s="88"/>
-      <c r="E152" s="34"/>
-      <c r="F152" s="34"/>
-      <c r="G152" s="34"/>
-      <c r="H152" s="87"/>
-      <c r="I152" s="91"/>
-      <c r="J152" s="23"/>
-      <c r="K152" s="23"/>
-      <c r="L152" s="23"/>
-      <c r="M152" s="23"/>
-      <c r="N152" s="23"/>
-      <c r="O152" s="23"/>
-      <c r="P152" s="23"/>
-      <c r="Q152" s="23"/>
+      <c r="A152" s="98"/>
+      <c r="B152" s="99"/>
+      <c r="C152" s="98"/>
+      <c r="D152" s="99"/>
+      <c r="E152" s="98"/>
+      <c r="F152" s="100"/>
+      <c r="G152" s="99"/>
+      <c r="H152" s="98"/>
+      <c r="I152" s="99"/>
+      <c r="J152" s="22"/>
+      <c r="K152" s="22"/>
+      <c r="L152" s="22"/>
+      <c r="M152" s="22"/>
+      <c r="N152" s="22"/>
+      <c r="O152" s="22"/>
+      <c r="P152" s="22"/>
+      <c r="Q152" s="22"/>
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
       <c r="T152" s="1"/>
@@ -6206,23 +6194,23 @@
       <c r="Z152" s="1"/>
     </row>
     <row r="153" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="28"/>
-      <c r="B153" s="34"/>
-      <c r="C153" s="87"/>
-      <c r="D153" s="88"/>
-      <c r="E153" s="34"/>
-      <c r="F153" s="34"/>
-      <c r="G153" s="34"/>
-      <c r="H153" s="87"/>
-      <c r="I153" s="91"/>
-      <c r="J153" s="23"/>
-      <c r="K153" s="23"/>
-      <c r="L153" s="23"/>
-      <c r="M153" s="23"/>
-      <c r="N153" s="23"/>
-      <c r="O153" s="23"/>
-      <c r="P153" s="23"/>
-      <c r="Q153" s="23"/>
+      <c r="A153" s="98"/>
+      <c r="B153" s="99"/>
+      <c r="C153" s="98"/>
+      <c r="D153" s="99"/>
+      <c r="E153" s="98"/>
+      <c r="F153" s="100"/>
+      <c r="G153" s="99"/>
+      <c r="H153" s="98"/>
+      <c r="I153" s="99"/>
+      <c r="J153" s="22"/>
+      <c r="K153" s="22"/>
+      <c r="L153" s="22"/>
+      <c r="M153" s="22"/>
+      <c r="N153" s="22"/>
+      <c r="O153" s="22"/>
+      <c r="P153" s="22"/>
+      <c r="Q153" s="22"/>
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
       <c r="T153" s="1"/>
@@ -6234,23 +6222,23 @@
       <c r="Z153" s="1"/>
     </row>
     <row r="154" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="30"/>
-      <c r="B154" s="35"/>
-      <c r="C154" s="89"/>
-      <c r="D154" s="90"/>
-      <c r="E154" s="35"/>
-      <c r="F154" s="35"/>
-      <c r="G154" s="35"/>
-      <c r="H154" s="89"/>
-      <c r="I154" s="90"/>
-      <c r="J154" s="23"/>
-      <c r="K154" s="23"/>
-      <c r="L154" s="23"/>
-      <c r="M154" s="23"/>
-      <c r="N154" s="23"/>
-      <c r="O154" s="23"/>
-      <c r="P154" s="23"/>
-      <c r="Q154" s="23"/>
+      <c r="A154" s="98"/>
+      <c r="B154" s="99"/>
+      <c r="C154" s="98"/>
+      <c r="D154" s="99"/>
+      <c r="E154" s="98"/>
+      <c r="F154" s="100"/>
+      <c r="G154" s="99"/>
+      <c r="H154" s="98"/>
+      <c r="I154" s="99"/>
+      <c r="J154" s="22"/>
+      <c r="K154" s="22"/>
+      <c r="L154" s="22"/>
+      <c r="M154" s="22"/>
+      <c r="N154" s="22"/>
+      <c r="O154" s="22"/>
+      <c r="P154" s="22"/>
+      <c r="Q154" s="22"/>
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
       <c r="T154" s="1"/>
@@ -6262,31 +6250,23 @@
       <c r="Z154" s="1"/>
     </row>
     <row r="155" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="42" t="s">
-        <v>155</v>
-      </c>
-      <c r="B155" s="39"/>
-      <c r="C155" s="84" t="s">
-        <v>156</v>
-      </c>
-      <c r="D155" s="54"/>
-      <c r="E155" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="F155" s="38"/>
-      <c r="G155" s="39"/>
-      <c r="H155" s="84" t="s">
-        <v>158</v>
-      </c>
-      <c r="I155" s="54"/>
-      <c r="J155" s="23"/>
-      <c r="K155" s="23"/>
-      <c r="L155" s="23"/>
-      <c r="M155" s="23"/>
-      <c r="N155" s="23"/>
-      <c r="O155" s="23"/>
-      <c r="P155" s="23"/>
-      <c r="Q155" s="23"/>
+      <c r="A155" s="98"/>
+      <c r="B155" s="99"/>
+      <c r="C155" s="98"/>
+      <c r="D155" s="99"/>
+      <c r="E155" s="98"/>
+      <c r="F155" s="100"/>
+      <c r="G155" s="99"/>
+      <c r="H155" s="98"/>
+      <c r="I155" s="99"/>
+      <c r="J155" s="22"/>
+      <c r="K155" s="22"/>
+      <c r="L155" s="22"/>
+      <c r="M155" s="22"/>
+      <c r="N155" s="22"/>
+      <c r="O155" s="22"/>
+      <c r="P155" s="22"/>
+      <c r="Q155" s="22"/>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
       <c r="T155" s="1"/>
@@ -6298,23 +6278,23 @@
       <c r="Z155" s="1"/>
     </row>
     <row r="156" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="36"/>
-      <c r="B156" s="27"/>
-      <c r="C156" s="36"/>
-      <c r="D156" s="27"/>
-      <c r="E156" s="36"/>
-      <c r="F156" s="33"/>
-      <c r="G156" s="27"/>
-      <c r="H156" s="36"/>
-      <c r="I156" s="27"/>
-      <c r="J156" s="23"/>
-      <c r="K156" s="23"/>
-      <c r="L156" s="23"/>
-      <c r="M156" s="23"/>
-      <c r="N156" s="23"/>
-      <c r="O156" s="23"/>
-      <c r="P156" s="23"/>
-      <c r="Q156" s="23"/>
+      <c r="A156" s="98"/>
+      <c r="B156" s="99"/>
+      <c r="C156" s="98"/>
+      <c r="D156" s="99"/>
+      <c r="E156" s="98"/>
+      <c r="F156" s="100"/>
+      <c r="G156" s="99"/>
+      <c r="H156" s="98"/>
+      <c r="I156" s="99"/>
+      <c r="J156" s="22"/>
+      <c r="K156" s="22"/>
+      <c r="L156" s="22"/>
+      <c r="M156" s="22"/>
+      <c r="N156" s="22"/>
+      <c r="O156" s="22"/>
+      <c r="P156" s="22"/>
+      <c r="Q156" s="22"/>
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
       <c r="T156" s="1"/>
@@ -6326,23 +6306,23 @@
       <c r="Z156" s="1"/>
     </row>
     <row r="157" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="28"/>
-      <c r="B157" s="29"/>
-      <c r="C157" s="28"/>
-      <c r="D157" s="29"/>
-      <c r="E157" s="28"/>
-      <c r="F157" s="34"/>
-      <c r="G157" s="29"/>
-      <c r="H157" s="28"/>
-      <c r="I157" s="29"/>
-      <c r="J157" s="23"/>
-      <c r="K157" s="23"/>
-      <c r="L157" s="23"/>
-      <c r="M157" s="23"/>
-      <c r="N157" s="23"/>
-      <c r="O157" s="23"/>
-      <c r="P157" s="23"/>
-      <c r="Q157" s="23"/>
+      <c r="A157" s="98"/>
+      <c r="B157" s="99"/>
+      <c r="C157" s="98"/>
+      <c r="D157" s="99"/>
+      <c r="E157" s="98"/>
+      <c r="F157" s="100"/>
+      <c r="G157" s="99"/>
+      <c r="H157" s="98"/>
+      <c r="I157" s="99"/>
+      <c r="J157" s="22"/>
+      <c r="K157" s="22"/>
+      <c r="L157" s="22"/>
+      <c r="M157" s="22"/>
+      <c r="N157" s="22"/>
+      <c r="O157" s="22"/>
+      <c r="P157" s="22"/>
+      <c r="Q157" s="22"/>
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
       <c r="T157" s="1"/>
@@ -6354,23 +6334,23 @@
       <c r="Z157" s="1"/>
     </row>
     <row r="158" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="28"/>
-      <c r="B158" s="29"/>
-      <c r="C158" s="28"/>
-      <c r="D158" s="29"/>
-      <c r="E158" s="28"/>
-      <c r="F158" s="34"/>
-      <c r="G158" s="29"/>
-      <c r="H158" s="28"/>
-      <c r="I158" s="29"/>
-      <c r="J158" s="23"/>
-      <c r="K158" s="23"/>
-      <c r="L158" s="23"/>
-      <c r="M158" s="23"/>
-      <c r="N158" s="23"/>
-      <c r="O158" s="23"/>
-      <c r="P158" s="23"/>
-      <c r="Q158" s="23"/>
+      <c r="A158" s="98"/>
+      <c r="B158" s="99"/>
+      <c r="C158" s="98"/>
+      <c r="D158" s="99"/>
+      <c r="E158" s="98"/>
+      <c r="F158" s="100"/>
+      <c r="G158" s="99"/>
+      <c r="H158" s="98"/>
+      <c r="I158" s="99"/>
+      <c r="J158" s="22"/>
+      <c r="K158" s="22"/>
+      <c r="L158" s="22"/>
+      <c r="M158" s="22"/>
+      <c r="N158" s="22"/>
+      <c r="O158" s="22"/>
+      <c r="P158" s="22"/>
+      <c r="Q158" s="22"/>
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
       <c r="T158" s="1"/>
@@ -6382,23 +6362,23 @@
       <c r="Z158" s="1"/>
     </row>
     <row r="159" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="28"/>
-      <c r="B159" s="29"/>
-      <c r="C159" s="28"/>
-      <c r="D159" s="29"/>
-      <c r="E159" s="28"/>
-      <c r="F159" s="34"/>
-      <c r="G159" s="29"/>
-      <c r="H159" s="28"/>
-      <c r="I159" s="29"/>
-      <c r="J159" s="23"/>
-      <c r="K159" s="23"/>
-      <c r="L159" s="23"/>
-      <c r="M159" s="23"/>
-      <c r="N159" s="23"/>
-      <c r="O159" s="23"/>
-      <c r="P159" s="23"/>
-      <c r="Q159" s="23"/>
+      <c r="A159" s="101"/>
+      <c r="B159" s="102"/>
+      <c r="C159" s="101"/>
+      <c r="D159" s="102"/>
+      <c r="E159" s="101"/>
+      <c r="F159" s="103"/>
+      <c r="G159" s="102"/>
+      <c r="H159" s="101"/>
+      <c r="I159" s="102"/>
+      <c r="J159" s="22"/>
+      <c r="K159" s="22"/>
+      <c r="L159" s="22"/>
+      <c r="M159" s="22"/>
+      <c r="N159" s="22"/>
+      <c r="O159" s="22"/>
+      <c r="P159" s="22"/>
+      <c r="Q159" s="22"/>
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
       <c r="T159" s="1"/>
@@ -6410,51 +6390,53 @@
       <c r="Z159" s="1"/>
     </row>
     <row r="160" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="28"/>
-      <c r="B160" s="29"/>
-      <c r="C160" s="28"/>
-      <c r="D160" s="29"/>
-      <c r="E160" s="28"/>
-      <c r="F160" s="34"/>
-      <c r="G160" s="29"/>
-      <c r="H160" s="28"/>
-      <c r="I160" s="29"/>
-      <c r="J160" s="23"/>
-      <c r="K160" s="23"/>
-      <c r="L160" s="23"/>
-      <c r="M160" s="23"/>
-      <c r="N160" s="23"/>
-      <c r="O160" s="23"/>
-      <c r="P160" s="23"/>
-      <c r="Q160" s="23"/>
-      <c r="R160" s="1"/>
-      <c r="S160" s="1"/>
-      <c r="T160" s="1"/>
-      <c r="U160" s="1"/>
-      <c r="V160" s="1"/>
-      <c r="W160" s="1"/>
-      <c r="X160" s="1"/>
-      <c r="Y160" s="1"/>
-      <c r="Z160" s="1"/>
+      <c r="A160" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="B160" s="40"/>
+      <c r="C160" s="40"/>
+      <c r="D160" s="40"/>
+      <c r="E160" s="40"/>
+      <c r="F160" s="40"/>
+      <c r="G160" s="40"/>
+      <c r="H160" s="40"/>
+      <c r="I160" s="41"/>
+      <c r="J160" s="22"/>
+      <c r="K160" s="22"/>
+      <c r="L160" s="22"/>
+      <c r="M160" s="22"/>
+      <c r="N160" s="22"/>
+      <c r="O160" s="22"/>
+      <c r="P160" s="22"/>
+      <c r="Q160" s="22"/>
+      <c r="R160" s="23"/>
+      <c r="S160" s="23"/>
+      <c r="T160" s="23"/>
+      <c r="U160" s="23"/>
+      <c r="V160" s="23"/>
+      <c r="W160" s="23"/>
+      <c r="X160" s="23"/>
+      <c r="Y160" s="23"/>
+      <c r="Z160" s="23"/>
     </row>
     <row r="161" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="28"/>
-      <c r="B161" s="29"/>
-      <c r="C161" s="28"/>
-      <c r="D161" s="29"/>
-      <c r="E161" s="28"/>
-      <c r="F161" s="34"/>
-      <c r="G161" s="29"/>
-      <c r="H161" s="28"/>
-      <c r="I161" s="29"/>
-      <c r="J161" s="23"/>
-      <c r="K161" s="23"/>
-      <c r="L161" s="23"/>
-      <c r="M161" s="23"/>
-      <c r="N161" s="23"/>
-      <c r="O161" s="23"/>
-      <c r="P161" s="23"/>
-      <c r="Q161" s="23"/>
+      <c r="A161" s="112"/>
+      <c r="B161" s="97"/>
+      <c r="C161" s="96"/>
+      <c r="D161" s="112"/>
+      <c r="E161" s="97"/>
+      <c r="F161" s="96"/>
+      <c r="G161" s="112"/>
+      <c r="H161" s="97"/>
+      <c r="I161" s="96"/>
+      <c r="J161" s="22"/>
+      <c r="K161" s="22"/>
+      <c r="L161" s="22"/>
+      <c r="M161" s="22"/>
+      <c r="N161" s="22"/>
+      <c r="O161" s="22"/>
+      <c r="P161" s="22"/>
+      <c r="Q161" s="22"/>
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
       <c r="T161" s="1"/>
@@ -6466,23 +6448,23 @@
       <c r="Z161" s="1"/>
     </row>
     <row r="162" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="28"/>
-      <c r="B162" s="29"/>
-      <c r="C162" s="28"/>
-      <c r="D162" s="29"/>
-      <c r="E162" s="28"/>
-      <c r="F162" s="34"/>
-      <c r="G162" s="29"/>
-      <c r="H162" s="28"/>
-      <c r="I162" s="29"/>
-      <c r="J162" s="23"/>
-      <c r="K162" s="23"/>
-      <c r="L162" s="23"/>
-      <c r="M162" s="23"/>
-      <c r="N162" s="23"/>
-      <c r="O162" s="23"/>
-      <c r="P162" s="23"/>
-      <c r="Q162" s="23"/>
+      <c r="A162" s="98"/>
+      <c r="B162" s="100"/>
+      <c r="C162" s="99"/>
+      <c r="D162" s="98"/>
+      <c r="E162" s="100"/>
+      <c r="F162" s="99"/>
+      <c r="G162" s="98"/>
+      <c r="H162" s="100"/>
+      <c r="I162" s="99"/>
+      <c r="J162" s="22"/>
+      <c r="K162" s="22"/>
+      <c r="L162" s="22"/>
+      <c r="M162" s="22"/>
+      <c r="N162" s="22"/>
+      <c r="O162" s="22"/>
+      <c r="P162" s="22"/>
+      <c r="Q162" s="22"/>
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
       <c r="T162" s="1"/>
@@ -6494,23 +6476,23 @@
       <c r="Z162" s="1"/>
     </row>
     <row r="163" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="28"/>
-      <c r="B163" s="29"/>
-      <c r="C163" s="28"/>
-      <c r="D163" s="29"/>
-      <c r="E163" s="28"/>
-      <c r="F163" s="34"/>
-      <c r="G163" s="29"/>
-      <c r="H163" s="28"/>
-      <c r="I163" s="29"/>
-      <c r="J163" s="23"/>
-      <c r="K163" s="23"/>
-      <c r="L163" s="23"/>
-      <c r="M163" s="23"/>
-      <c r="N163" s="23"/>
-      <c r="O163" s="23"/>
-      <c r="P163" s="23"/>
-      <c r="Q163" s="23"/>
+      <c r="A163" s="98"/>
+      <c r="B163" s="100"/>
+      <c r="C163" s="99"/>
+      <c r="D163" s="98"/>
+      <c r="E163" s="100"/>
+      <c r="F163" s="99"/>
+      <c r="G163" s="98"/>
+      <c r="H163" s="100"/>
+      <c r="I163" s="99"/>
+      <c r="J163" s="22"/>
+      <c r="K163" s="22"/>
+      <c r="L163" s="22"/>
+      <c r="M163" s="22"/>
+      <c r="N163" s="22"/>
+      <c r="O163" s="22"/>
+      <c r="P163" s="22"/>
+      <c r="Q163" s="22"/>
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
       <c r="T163" s="1"/>
@@ -6522,23 +6504,23 @@
       <c r="Z163" s="1"/>
     </row>
     <row r="164" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="28"/>
-      <c r="B164" s="29"/>
-      <c r="C164" s="28"/>
-      <c r="D164" s="29"/>
-      <c r="E164" s="28"/>
-      <c r="F164" s="34"/>
-      <c r="G164" s="29"/>
-      <c r="H164" s="28"/>
-      <c r="I164" s="29"/>
-      <c r="J164" s="23"/>
-      <c r="K164" s="23"/>
-      <c r="L164" s="23"/>
-      <c r="M164" s="23"/>
-      <c r="N164" s="23"/>
-      <c r="O164" s="23"/>
-      <c r="P164" s="23"/>
-      <c r="Q164" s="23"/>
+      <c r="A164" s="98"/>
+      <c r="B164" s="100"/>
+      <c r="C164" s="99"/>
+      <c r="D164" s="98"/>
+      <c r="E164" s="100"/>
+      <c r="F164" s="99"/>
+      <c r="G164" s="98"/>
+      <c r="H164" s="100"/>
+      <c r="I164" s="99"/>
+      <c r="J164" s="22"/>
+      <c r="K164" s="22"/>
+      <c r="L164" s="22"/>
+      <c r="M164" s="22"/>
+      <c r="N164" s="22"/>
+      <c r="O164" s="22"/>
+      <c r="P164" s="22"/>
+      <c r="Q164" s="22"/>
       <c r="R164" s="1"/>
       <c r="S164" s="1"/>
       <c r="T164" s="1"/>
@@ -6550,23 +6532,23 @@
       <c r="Z164" s="1"/>
     </row>
     <row r="165" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="28"/>
-      <c r="B165" s="29"/>
-      <c r="C165" s="28"/>
-      <c r="D165" s="29"/>
-      <c r="E165" s="28"/>
-      <c r="F165" s="34"/>
-      <c r="G165" s="29"/>
-      <c r="H165" s="28"/>
-      <c r="I165" s="29"/>
-      <c r="J165" s="23"/>
-      <c r="K165" s="23"/>
-      <c r="L165" s="23"/>
-      <c r="M165" s="23"/>
-      <c r="N165" s="23"/>
-      <c r="O165" s="23"/>
-      <c r="P165" s="23"/>
-      <c r="Q165" s="23"/>
+      <c r="A165" s="98"/>
+      <c r="B165" s="100"/>
+      <c r="C165" s="99"/>
+      <c r="D165" s="98"/>
+      <c r="E165" s="100"/>
+      <c r="F165" s="99"/>
+      <c r="G165" s="98"/>
+      <c r="H165" s="100"/>
+      <c r="I165" s="99"/>
+      <c r="J165" s="22"/>
+      <c r="K165" s="22"/>
+      <c r="L165" s="22"/>
+      <c r="M165" s="22"/>
+      <c r="N165" s="22"/>
+      <c r="O165" s="22"/>
+      <c r="P165" s="22"/>
+      <c r="Q165" s="22"/>
       <c r="R165" s="1"/>
       <c r="S165" s="1"/>
       <c r="T165" s="1"/>
@@ -6578,23 +6560,23 @@
       <c r="Z165" s="1"/>
     </row>
     <row r="166" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="28"/>
-      <c r="B166" s="29"/>
-      <c r="C166" s="28"/>
-      <c r="D166" s="29"/>
-      <c r="E166" s="28"/>
-      <c r="F166" s="34"/>
-      <c r="G166" s="29"/>
-      <c r="H166" s="28"/>
-      <c r="I166" s="29"/>
-      <c r="J166" s="23"/>
-      <c r="K166" s="23"/>
-      <c r="L166" s="23"/>
-      <c r="M166" s="23"/>
-      <c r="N166" s="23"/>
-      <c r="O166" s="23"/>
-      <c r="P166" s="23"/>
-      <c r="Q166" s="23"/>
+      <c r="A166" s="98"/>
+      <c r="B166" s="100"/>
+      <c r="C166" s="99"/>
+      <c r="D166" s="98"/>
+      <c r="E166" s="100"/>
+      <c r="F166" s="99"/>
+      <c r="G166" s="98"/>
+      <c r="H166" s="100"/>
+      <c r="I166" s="99"/>
+      <c r="J166" s="22"/>
+      <c r="K166" s="22"/>
+      <c r="L166" s="22"/>
+      <c r="M166" s="22"/>
+      <c r="N166" s="22"/>
+      <c r="O166" s="22"/>
+      <c r="P166" s="22"/>
+      <c r="Q166" s="22"/>
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
       <c r="T166" s="1"/>
@@ -6606,23 +6588,23 @@
       <c r="Z166" s="1"/>
     </row>
     <row r="167" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="30"/>
-      <c r="B167" s="31"/>
-      <c r="C167" s="30"/>
-      <c r="D167" s="31"/>
-      <c r="E167" s="30"/>
-      <c r="F167" s="35"/>
-      <c r="G167" s="31"/>
-      <c r="H167" s="30"/>
-      <c r="I167" s="31"/>
-      <c r="J167" s="23"/>
-      <c r="K167" s="23"/>
-      <c r="L167" s="23"/>
-      <c r="M167" s="23"/>
-      <c r="N167" s="23"/>
-      <c r="O167" s="23"/>
-      <c r="P167" s="23"/>
-      <c r="Q167" s="23"/>
+      <c r="A167" s="98"/>
+      <c r="B167" s="100"/>
+      <c r="C167" s="99"/>
+      <c r="D167" s="98"/>
+      <c r="E167" s="100"/>
+      <c r="F167" s="99"/>
+      <c r="G167" s="98"/>
+      <c r="H167" s="100"/>
+      <c r="I167" s="99"/>
+      <c r="J167" s="22"/>
+      <c r="K167" s="22"/>
+      <c r="L167" s="22"/>
+      <c r="M167" s="22"/>
+      <c r="N167" s="22"/>
+      <c r="O167" s="22"/>
+      <c r="P167" s="22"/>
+      <c r="Q167" s="22"/>
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
       <c r="T167" s="1"/>
@@ -6634,53 +6616,51 @@
       <c r="Z167" s="1"/>
     </row>
     <row r="168" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="43" t="s">
-        <v>159</v>
-      </c>
-      <c r="B168" s="38"/>
-      <c r="C168" s="38"/>
-      <c r="D168" s="38"/>
-      <c r="E168" s="38"/>
-      <c r="F168" s="38"/>
-      <c r="G168" s="38"/>
-      <c r="H168" s="38"/>
-      <c r="I168" s="39"/>
-      <c r="J168" s="23"/>
-      <c r="K168" s="23"/>
-      <c r="L168" s="23"/>
-      <c r="M168" s="23"/>
-      <c r="N168" s="23"/>
-      <c r="O168" s="23"/>
-      <c r="P168" s="23"/>
-      <c r="Q168" s="23"/>
-      <c r="R168" s="24"/>
-      <c r="S168" s="24"/>
-      <c r="T168" s="24"/>
-      <c r="U168" s="24"/>
-      <c r="V168" s="24"/>
-      <c r="W168" s="24"/>
-      <c r="X168" s="24"/>
-      <c r="Y168" s="24"/>
-      <c r="Z168" s="24"/>
+      <c r="A168" s="98"/>
+      <c r="B168" s="100"/>
+      <c r="C168" s="99"/>
+      <c r="D168" s="98"/>
+      <c r="E168" s="100"/>
+      <c r="F168" s="99"/>
+      <c r="G168" s="98"/>
+      <c r="H168" s="100"/>
+      <c r="I168" s="99"/>
+      <c r="J168" s="22"/>
+      <c r="K168" s="22"/>
+      <c r="L168" s="22"/>
+      <c r="M168" s="22"/>
+      <c r="N168" s="22"/>
+      <c r="O168" s="22"/>
+      <c r="P168" s="22"/>
+      <c r="Q168" s="22"/>
+      <c r="R168" s="1"/>
+      <c r="S168" s="1"/>
+      <c r="T168" s="1"/>
+      <c r="U168" s="1"/>
+      <c r="V168" s="1"/>
+      <c r="W168" s="1"/>
+      <c r="X168" s="1"/>
+      <c r="Y168" s="1"/>
+      <c r="Z168" s="1"/>
     </row>
     <row r="169" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="26"/>
-      <c r="B169" s="33"/>
-      <c r="C169" s="27"/>
-      <c r="D169" s="26"/>
-      <c r="E169" s="33"/>
-      <c r="F169" s="27"/>
-      <c r="G169" s="26"/>
-      <c r="H169" s="33"/>
-      <c r="I169" s="27"/>
-      <c r="J169" s="23"/>
-      <c r="K169" s="23"/>
-      <c r="L169" s="23"/>
-      <c r="M169" s="23"/>
-      <c r="N169" s="23"/>
-      <c r="O169" s="23"/>
-      <c r="P169" s="23"/>
-      <c r="Q169" s="23"/>
+      <c r="A169" s="98"/>
+      <c r="B169" s="100"/>
+      <c r="C169" s="99"/>
+      <c r="D169" s="98"/>
+      <c r="E169" s="100"/>
+      <c r="F169" s="99"/>
+      <c r="G169" s="98"/>
+      <c r="H169" s="100"/>
+      <c r="I169" s="99"/>
+      <c r="J169" s="22"/>
+      <c r="K169" s="22"/>
+      <c r="L169" s="22"/>
+      <c r="M169" s="22"/>
+      <c r="N169" s="22"/>
+      <c r="O169" s="22"/>
+      <c r="P169" s="22"/>
+      <c r="Q169" s="22"/>
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
       <c r="T169" s="1"/>
@@ -6692,23 +6672,23 @@
       <c r="Z169" s="1"/>
     </row>
     <row r="170" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="28"/>
-      <c r="B170" s="34"/>
-      <c r="C170" s="29"/>
-      <c r="D170" s="28"/>
-      <c r="E170" s="34"/>
-      <c r="F170" s="29"/>
-      <c r="G170" s="28"/>
-      <c r="H170" s="34"/>
-      <c r="I170" s="29"/>
-      <c r="J170" s="23"/>
-      <c r="K170" s="23"/>
-      <c r="L170" s="23"/>
-      <c r="M170" s="23"/>
-      <c r="N170" s="23"/>
-      <c r="O170" s="23"/>
-      <c r="P170" s="23"/>
-      <c r="Q170" s="23"/>
+      <c r="A170" s="98"/>
+      <c r="B170" s="100"/>
+      <c r="C170" s="99"/>
+      <c r="D170" s="98"/>
+      <c r="E170" s="100"/>
+      <c r="F170" s="99"/>
+      <c r="G170" s="98"/>
+      <c r="H170" s="100"/>
+      <c r="I170" s="99"/>
+      <c r="J170" s="22"/>
+      <c r="K170" s="22"/>
+      <c r="L170" s="22"/>
+      <c r="M170" s="22"/>
+      <c r="N170" s="22"/>
+      <c r="O170" s="22"/>
+      <c r="P170" s="22"/>
+      <c r="Q170" s="22"/>
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
       <c r="T170" s="1"/>
@@ -6720,23 +6700,23 @@
       <c r="Z170" s="1"/>
     </row>
     <row r="171" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="28"/>
-      <c r="B171" s="34"/>
-      <c r="C171" s="29"/>
-      <c r="D171" s="28"/>
-      <c r="E171" s="34"/>
-      <c r="F171" s="29"/>
-      <c r="G171" s="28"/>
-      <c r="H171" s="34"/>
-      <c r="I171" s="29"/>
-      <c r="J171" s="23"/>
-      <c r="K171" s="23"/>
-      <c r="L171" s="23"/>
-      <c r="M171" s="23"/>
-      <c r="N171" s="23"/>
-      <c r="O171" s="23"/>
-      <c r="P171" s="23"/>
-      <c r="Q171" s="23"/>
+      <c r="A171" s="98"/>
+      <c r="B171" s="100"/>
+      <c r="C171" s="99"/>
+      <c r="D171" s="98"/>
+      <c r="E171" s="100"/>
+      <c r="F171" s="99"/>
+      <c r="G171" s="98"/>
+      <c r="H171" s="100"/>
+      <c r="I171" s="99"/>
+      <c r="J171" s="22"/>
+      <c r="K171" s="22"/>
+      <c r="L171" s="22"/>
+      <c r="M171" s="22"/>
+      <c r="N171" s="22"/>
+      <c r="O171" s="22"/>
+      <c r="P171" s="22"/>
+      <c r="Q171" s="22"/>
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
       <c r="T171" s="1"/>
@@ -6748,23 +6728,23 @@
       <c r="Z171" s="1"/>
     </row>
     <row r="172" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="28"/>
-      <c r="B172" s="34"/>
-      <c r="C172" s="29"/>
-      <c r="D172" s="28"/>
-      <c r="E172" s="34"/>
-      <c r="F172" s="29"/>
-      <c r="G172" s="28"/>
-      <c r="H172" s="34"/>
-      <c r="I172" s="29"/>
-      <c r="J172" s="23"/>
-      <c r="K172" s="23"/>
-      <c r="L172" s="23"/>
-      <c r="M172" s="23"/>
-      <c r="N172" s="23"/>
-      <c r="O172" s="23"/>
-      <c r="P172" s="23"/>
-      <c r="Q172" s="23"/>
+      <c r="A172" s="98"/>
+      <c r="B172" s="100"/>
+      <c r="C172" s="99"/>
+      <c r="D172" s="98"/>
+      <c r="E172" s="100"/>
+      <c r="F172" s="99"/>
+      <c r="G172" s="98"/>
+      <c r="H172" s="100"/>
+      <c r="I172" s="99"/>
+      <c r="J172" s="22"/>
+      <c r="K172" s="22"/>
+      <c r="L172" s="22"/>
+      <c r="M172" s="22"/>
+      <c r="N172" s="22"/>
+      <c r="O172" s="22"/>
+      <c r="P172" s="22"/>
+      <c r="Q172" s="22"/>
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
       <c r="T172" s="1"/>
@@ -6776,23 +6756,23 @@
       <c r="Z172" s="1"/>
     </row>
     <row r="173" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="28"/>
-      <c r="B173" s="34"/>
-      <c r="C173" s="29"/>
-      <c r="D173" s="28"/>
-      <c r="E173" s="34"/>
-      <c r="F173" s="29"/>
-      <c r="G173" s="28"/>
-      <c r="H173" s="34"/>
-      <c r="I173" s="29"/>
-      <c r="J173" s="23"/>
-      <c r="K173" s="23"/>
-      <c r="L173" s="23"/>
-      <c r="M173" s="23"/>
-      <c r="N173" s="23"/>
-      <c r="O173" s="23"/>
-      <c r="P173" s="23"/>
-      <c r="Q173" s="23"/>
+      <c r="A173" s="98"/>
+      <c r="B173" s="100"/>
+      <c r="C173" s="99"/>
+      <c r="D173" s="98"/>
+      <c r="E173" s="100"/>
+      <c r="F173" s="99"/>
+      <c r="G173" s="98"/>
+      <c r="H173" s="100"/>
+      <c r="I173" s="99"/>
+      <c r="J173" s="22"/>
+      <c r="K173" s="22"/>
+      <c r="L173" s="22"/>
+      <c r="M173" s="22"/>
+      <c r="N173" s="22"/>
+      <c r="O173" s="22"/>
+      <c r="P173" s="22"/>
+      <c r="Q173" s="22"/>
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
       <c r="T173" s="1"/>
@@ -6804,23 +6784,23 @@
       <c r="Z173" s="1"/>
     </row>
     <row r="174" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="28"/>
-      <c r="B174" s="34"/>
-      <c r="C174" s="29"/>
-      <c r="D174" s="28"/>
-      <c r="E174" s="34"/>
-      <c r="F174" s="29"/>
-      <c r="G174" s="28"/>
-      <c r="H174" s="34"/>
-      <c r="I174" s="29"/>
-      <c r="J174" s="23"/>
-      <c r="K174" s="23"/>
-      <c r="L174" s="23"/>
-      <c r="M174" s="23"/>
-      <c r="N174" s="23"/>
-      <c r="O174" s="23"/>
-      <c r="P174" s="23"/>
-      <c r="Q174" s="23"/>
+      <c r="A174" s="98"/>
+      <c r="B174" s="100"/>
+      <c r="C174" s="99"/>
+      <c r="D174" s="98"/>
+      <c r="E174" s="100"/>
+      <c r="F174" s="99"/>
+      <c r="G174" s="98"/>
+      <c r="H174" s="100"/>
+      <c r="I174" s="99"/>
+      <c r="J174" s="22"/>
+      <c r="K174" s="22"/>
+      <c r="L174" s="22"/>
+      <c r="M174" s="22"/>
+      <c r="N174" s="22"/>
+      <c r="O174" s="22"/>
+      <c r="P174" s="22"/>
+      <c r="Q174" s="22"/>
       <c r="R174" s="1"/>
       <c r="S174" s="1"/>
       <c r="T174" s="1"/>
@@ -6832,23 +6812,23 @@
       <c r="Z174" s="1"/>
     </row>
     <row r="175" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="28"/>
-      <c r="B175" s="34"/>
-      <c r="C175" s="29"/>
-      <c r="D175" s="28"/>
-      <c r="E175" s="34"/>
-      <c r="F175" s="29"/>
-      <c r="G175" s="28"/>
-      <c r="H175" s="34"/>
-      <c r="I175" s="29"/>
-      <c r="J175" s="23"/>
-      <c r="K175" s="23"/>
-      <c r="L175" s="23"/>
-      <c r="M175" s="23"/>
-      <c r="N175" s="23"/>
-      <c r="O175" s="23"/>
-      <c r="P175" s="23"/>
-      <c r="Q175" s="23"/>
+      <c r="A175" s="98"/>
+      <c r="B175" s="100"/>
+      <c r="C175" s="99"/>
+      <c r="D175" s="98"/>
+      <c r="E175" s="100"/>
+      <c r="F175" s="99"/>
+      <c r="G175" s="98"/>
+      <c r="H175" s="100"/>
+      <c r="I175" s="99"/>
+      <c r="J175" s="22"/>
+      <c r="K175" s="22"/>
+      <c r="L175" s="22"/>
+      <c r="M175" s="22"/>
+      <c r="N175" s="22"/>
+      <c r="O175" s="22"/>
+      <c r="P175" s="22"/>
+      <c r="Q175" s="22"/>
       <c r="R175" s="1"/>
       <c r="S175" s="1"/>
       <c r="T175" s="1"/>
@@ -6860,23 +6840,23 @@
       <c r="Z175" s="1"/>
     </row>
     <row r="176" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="28"/>
-      <c r="B176" s="34"/>
-      <c r="C176" s="29"/>
-      <c r="D176" s="28"/>
-      <c r="E176" s="34"/>
-      <c r="F176" s="29"/>
-      <c r="G176" s="28"/>
-      <c r="H176" s="34"/>
-      <c r="I176" s="29"/>
-      <c r="J176" s="23"/>
-      <c r="K176" s="23"/>
-      <c r="L176" s="23"/>
-      <c r="M176" s="23"/>
-      <c r="N176" s="23"/>
-      <c r="O176" s="23"/>
-      <c r="P176" s="23"/>
-      <c r="Q176" s="23"/>
+      <c r="A176" s="98"/>
+      <c r="B176" s="100"/>
+      <c r="C176" s="99"/>
+      <c r="D176" s="98"/>
+      <c r="E176" s="100"/>
+      <c r="F176" s="99"/>
+      <c r="G176" s="98"/>
+      <c r="H176" s="100"/>
+      <c r="I176" s="99"/>
+      <c r="J176" s="22"/>
+      <c r="K176" s="22"/>
+      <c r="L176" s="22"/>
+      <c r="M176" s="22"/>
+      <c r="N176" s="22"/>
+      <c r="O176" s="22"/>
+      <c r="P176" s="22"/>
+      <c r="Q176" s="22"/>
       <c r="R176" s="1"/>
       <c r="S176" s="1"/>
       <c r="T176" s="1"/>
@@ -6888,23 +6868,23 @@
       <c r="Z176" s="1"/>
     </row>
     <row r="177" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="28"/>
-      <c r="B177" s="34"/>
-      <c r="C177" s="29"/>
-      <c r="D177" s="28"/>
-      <c r="E177" s="34"/>
-      <c r="F177" s="29"/>
-      <c r="G177" s="28"/>
-      <c r="H177" s="34"/>
-      <c r="I177" s="29"/>
-      <c r="J177" s="23"/>
-      <c r="K177" s="23"/>
-      <c r="L177" s="23"/>
-      <c r="M177" s="23"/>
-      <c r="N177" s="23"/>
-      <c r="O177" s="23"/>
-      <c r="P177" s="23"/>
-      <c r="Q177" s="23"/>
+      <c r="A177" s="98"/>
+      <c r="B177" s="100"/>
+      <c r="C177" s="99"/>
+      <c r="D177" s="98"/>
+      <c r="E177" s="100"/>
+      <c r="F177" s="99"/>
+      <c r="G177" s="98"/>
+      <c r="H177" s="100"/>
+      <c r="I177" s="99"/>
+      <c r="J177" s="22"/>
+      <c r="K177" s="22"/>
+      <c r="L177" s="22"/>
+      <c r="M177" s="22"/>
+      <c r="N177" s="22"/>
+      <c r="O177" s="22"/>
+      <c r="P177" s="22"/>
+      <c r="Q177" s="22"/>
       <c r="R177" s="1"/>
       <c r="S177" s="1"/>
       <c r="T177" s="1"/>
@@ -6915,24 +6895,26 @@
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
     </row>
-    <row r="178" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="28"/>
-      <c r="B178" s="34"/>
-      <c r="C178" s="29"/>
-      <c r="D178" s="28"/>
-      <c r="E178" s="34"/>
-      <c r="F178" s="29"/>
-      <c r="G178" s="28"/>
-      <c r="H178" s="34"/>
-      <c r="I178" s="29"/>
-      <c r="J178" s="23"/>
-      <c r="K178" s="23"/>
-      <c r="L178" s="23"/>
-      <c r="M178" s="23"/>
-      <c r="N178" s="23"/>
-      <c r="O178" s="23"/>
-      <c r="P178" s="23"/>
-      <c r="Q178" s="23"/>
+    <row r="178" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A178" s="98"/>
+      <c r="B178" s="100"/>
+      <c r="C178" s="99"/>
+      <c r="D178" s="98"/>
+      <c r="E178" s="100"/>
+      <c r="F178" s="99"/>
+      <c r="G178" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="H178" s="72"/>
+      <c r="I178" s="41"/>
+      <c r="J178" s="22"/>
+      <c r="K178" s="22"/>
+      <c r="L178" s="22"/>
+      <c r="M178" s="22"/>
+      <c r="N178" s="22"/>
+      <c r="O178" s="22"/>
+      <c r="P178" s="22"/>
+      <c r="Q178" s="22"/>
       <c r="R178" s="1"/>
       <c r="S178" s="1"/>
       <c r="T178" s="1"/>
@@ -6943,24 +6925,26 @@
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
     </row>
-    <row r="179" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="28"/>
-      <c r="B179" s="34"/>
-      <c r="C179" s="29"/>
-      <c r="D179" s="28"/>
-      <c r="E179" s="34"/>
-      <c r="F179" s="29"/>
-      <c r="G179" s="28"/>
-      <c r="H179" s="34"/>
-      <c r="I179" s="29"/>
-      <c r="J179" s="23"/>
-      <c r="K179" s="23"/>
-      <c r="L179" s="23"/>
-      <c r="M179" s="23"/>
-      <c r="N179" s="23"/>
-      <c r="O179" s="23"/>
-      <c r="P179" s="23"/>
-      <c r="Q179" s="23"/>
+    <row r="179" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A179" s="98"/>
+      <c r="B179" s="100"/>
+      <c r="C179" s="99"/>
+      <c r="D179" s="98"/>
+      <c r="E179" s="100"/>
+      <c r="F179" s="99"/>
+      <c r="G179" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H179" s="72"/>
+      <c r="I179" s="41"/>
+      <c r="J179" s="22"/>
+      <c r="K179" s="22"/>
+      <c r="L179" s="22"/>
+      <c r="M179" s="22"/>
+      <c r="N179" s="22"/>
+      <c r="O179" s="22"/>
+      <c r="P179" s="22"/>
+      <c r="Q179" s="22"/>
       <c r="R179" s="1"/>
       <c r="S179" s="1"/>
       <c r="T179" s="1"/>
@@ -6971,24 +6955,26 @@
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
     </row>
-    <row r="180" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="28"/>
-      <c r="B180" s="34"/>
-      <c r="C180" s="29"/>
-      <c r="D180" s="28"/>
-      <c r="E180" s="34"/>
-      <c r="F180" s="29"/>
-      <c r="G180" s="28"/>
-      <c r="H180" s="34"/>
-      <c r="I180" s="29"/>
-      <c r="J180" s="23"/>
-      <c r="K180" s="23"/>
-      <c r="L180" s="23"/>
-      <c r="M180" s="23"/>
-      <c r="N180" s="23"/>
-      <c r="O180" s="23"/>
-      <c r="P180" s="23"/>
-      <c r="Q180" s="23"/>
+    <row r="180" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A180" s="98"/>
+      <c r="B180" s="100"/>
+      <c r="C180" s="99"/>
+      <c r="D180" s="101"/>
+      <c r="E180" s="103"/>
+      <c r="F180" s="102"/>
+      <c r="G180" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="H180" s="72"/>
+      <c r="I180" s="41"/>
+      <c r="J180" s="22"/>
+      <c r="K180" s="22"/>
+      <c r="L180" s="22"/>
+      <c r="M180" s="22"/>
+      <c r="N180" s="22"/>
+      <c r="O180" s="22"/>
+      <c r="P180" s="22"/>
+      <c r="Q180" s="22"/>
       <c r="R180" s="1"/>
       <c r="S180" s="1"/>
       <c r="T180" s="1"/>
@@ -7000,23 +6986,29 @@
       <c r="Z180" s="1"/>
     </row>
     <row r="181" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="28"/>
-      <c r="B181" s="34"/>
-      <c r="C181" s="29"/>
-      <c r="D181" s="28"/>
-      <c r="E181" s="34"/>
-      <c r="F181" s="29"/>
-      <c r="G181" s="28"/>
-      <c r="H181" s="34"/>
-      <c r="I181" s="29"/>
-      <c r="J181" s="23"/>
-      <c r="K181" s="23"/>
-      <c r="L181" s="23"/>
-      <c r="M181" s="23"/>
-      <c r="N181" s="23"/>
-      <c r="O181" s="23"/>
-      <c r="P181" s="23"/>
-      <c r="Q181" s="23"/>
+      <c r="A181" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="B181" s="40"/>
+      <c r="C181" s="41"/>
+      <c r="D181" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="E181" s="40"/>
+      <c r="F181" s="41"/>
+      <c r="G181" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="H181" s="40"/>
+      <c r="I181" s="41"/>
+      <c r="J181" s="22"/>
+      <c r="K181" s="22"/>
+      <c r="L181" s="22"/>
+      <c r="M181" s="22"/>
+      <c r="N181" s="22"/>
+      <c r="O181" s="22"/>
+      <c r="P181" s="22"/>
+      <c r="Q181" s="22"/>
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
       <c r="T181" s="1"/>
@@ -7028,23 +7020,23 @@
       <c r="Z181" s="1"/>
     </row>
     <row r="182" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="28"/>
-      <c r="B182" s="34"/>
-      <c r="C182" s="29"/>
-      <c r="D182" s="28"/>
-      <c r="E182" s="34"/>
-      <c r="F182" s="29"/>
-      <c r="G182" s="28"/>
-      <c r="H182" s="34"/>
-      <c r="I182" s="29"/>
-      <c r="J182" s="23"/>
-      <c r="K182" s="23"/>
-      <c r="L182" s="23"/>
-      <c r="M182" s="23"/>
-      <c r="N182" s="23"/>
-      <c r="O182" s="23"/>
-      <c r="P182" s="23"/>
-      <c r="Q182" s="23"/>
+      <c r="A182" s="112"/>
+      <c r="B182" s="97"/>
+      <c r="C182" s="96"/>
+      <c r="D182" s="112"/>
+      <c r="E182" s="97"/>
+      <c r="F182" s="96"/>
+      <c r="G182" s="112"/>
+      <c r="H182" s="97"/>
+      <c r="I182" s="96"/>
+      <c r="J182" s="22"/>
+      <c r="K182" s="22"/>
+      <c r="L182" s="22"/>
+      <c r="M182" s="22"/>
+      <c r="N182" s="22"/>
+      <c r="O182" s="22"/>
+      <c r="P182" s="22"/>
+      <c r="Q182" s="22"/>
       <c r="R182" s="1"/>
       <c r="S182" s="1"/>
       <c r="T182" s="1"/>
@@ -7056,23 +7048,23 @@
       <c r="Z182" s="1"/>
     </row>
     <row r="183" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="28"/>
-      <c r="B183" s="34"/>
-      <c r="C183" s="29"/>
-      <c r="D183" s="28"/>
-      <c r="E183" s="34"/>
-      <c r="F183" s="29"/>
-      <c r="G183" s="28"/>
-      <c r="H183" s="34"/>
-      <c r="I183" s="29"/>
-      <c r="J183" s="23"/>
-      <c r="K183" s="23"/>
-      <c r="L183" s="23"/>
-      <c r="M183" s="23"/>
-      <c r="N183" s="23"/>
-      <c r="O183" s="23"/>
-      <c r="P183" s="23"/>
-      <c r="Q183" s="23"/>
+      <c r="A183" s="98"/>
+      <c r="B183" s="100"/>
+      <c r="C183" s="99"/>
+      <c r="D183" s="98"/>
+      <c r="E183" s="100"/>
+      <c r="F183" s="99"/>
+      <c r="G183" s="98"/>
+      <c r="H183" s="100"/>
+      <c r="I183" s="99"/>
+      <c r="J183" s="22"/>
+      <c r="K183" s="22"/>
+      <c r="L183" s="22"/>
+      <c r="M183" s="22"/>
+      <c r="N183" s="22"/>
+      <c r="O183" s="22"/>
+      <c r="P183" s="22"/>
+      <c r="Q183" s="22"/>
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
       <c r="T183" s="1"/>
@@ -7084,23 +7076,23 @@
       <c r="Z183" s="1"/>
     </row>
     <row r="184" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="28"/>
-      <c r="B184" s="34"/>
-      <c r="C184" s="29"/>
-      <c r="D184" s="28"/>
-      <c r="E184" s="34"/>
-      <c r="F184" s="29"/>
-      <c r="G184" s="28"/>
-      <c r="H184" s="34"/>
-      <c r="I184" s="29"/>
-      <c r="J184" s="23"/>
-      <c r="K184" s="23"/>
-      <c r="L184" s="23"/>
-      <c r="M184" s="23"/>
-      <c r="N184" s="23"/>
-      <c r="O184" s="23"/>
-      <c r="P184" s="23"/>
-      <c r="Q184" s="23"/>
+      <c r="A184" s="98"/>
+      <c r="B184" s="100"/>
+      <c r="C184" s="99"/>
+      <c r="D184" s="98"/>
+      <c r="E184" s="100"/>
+      <c r="F184" s="99"/>
+      <c r="G184" s="98"/>
+      <c r="H184" s="100"/>
+      <c r="I184" s="99"/>
+      <c r="J184" s="22"/>
+      <c r="K184" s="22"/>
+      <c r="L184" s="22"/>
+      <c r="M184" s="22"/>
+      <c r="N184" s="22"/>
+      <c r="O184" s="22"/>
+      <c r="P184" s="22"/>
+      <c r="Q184" s="22"/>
       <c r="R184" s="1"/>
       <c r="S184" s="1"/>
       <c r="T184" s="1"/>
@@ -7112,23 +7104,23 @@
       <c r="Z184" s="1"/>
     </row>
     <row r="185" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="28"/>
-      <c r="B185" s="34"/>
-      <c r="C185" s="29"/>
-      <c r="D185" s="28"/>
-      <c r="E185" s="34"/>
-      <c r="F185" s="29"/>
-      <c r="G185" s="28"/>
-      <c r="H185" s="34"/>
-      <c r="I185" s="29"/>
-      <c r="J185" s="23"/>
-      <c r="K185" s="23"/>
-      <c r="L185" s="23"/>
-      <c r="M185" s="23"/>
-      <c r="N185" s="23"/>
-      <c r="O185" s="23"/>
-      <c r="P185" s="23"/>
-      <c r="Q185" s="23"/>
+      <c r="A185" s="98"/>
+      <c r="B185" s="100"/>
+      <c r="C185" s="99"/>
+      <c r="D185" s="98"/>
+      <c r="E185" s="100"/>
+      <c r="F185" s="99"/>
+      <c r="G185" s="98"/>
+      <c r="H185" s="100"/>
+      <c r="I185" s="99"/>
+      <c r="J185" s="22"/>
+      <c r="K185" s="22"/>
+      <c r="L185" s="22"/>
+      <c r="M185" s="22"/>
+      <c r="N185" s="22"/>
+      <c r="O185" s="22"/>
+      <c r="P185" s="22"/>
+      <c r="Q185" s="22"/>
       <c r="R185" s="1"/>
       <c r="S185" s="1"/>
       <c r="T185" s="1"/>
@@ -7139,26 +7131,24 @@
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
     </row>
-    <row r="186" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A186" s="28"/>
-      <c r="B186" s="34"/>
-      <c r="C186" s="29"/>
-      <c r="D186" s="28"/>
-      <c r="E186" s="34"/>
-      <c r="F186" s="29"/>
-      <c r="G186" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="H186" s="44"/>
-      <c r="I186" s="39"/>
-      <c r="J186" s="23"/>
-      <c r="K186" s="23"/>
-      <c r="L186" s="23"/>
-      <c r="M186" s="23"/>
-      <c r="N186" s="23"/>
-      <c r="O186" s="23"/>
-      <c r="P186" s="23"/>
-      <c r="Q186" s="23"/>
+    <row r="186" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="98"/>
+      <c r="B186" s="100"/>
+      <c r="C186" s="99"/>
+      <c r="D186" s="98"/>
+      <c r="E186" s="100"/>
+      <c r="F186" s="99"/>
+      <c r="G186" s="98"/>
+      <c r="H186" s="100"/>
+      <c r="I186" s="99"/>
+      <c r="J186" s="22"/>
+      <c r="K186" s="22"/>
+      <c r="L186" s="22"/>
+      <c r="M186" s="22"/>
+      <c r="N186" s="22"/>
+      <c r="O186" s="22"/>
+      <c r="P186" s="22"/>
+      <c r="Q186" s="22"/>
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
       <c r="T186" s="1"/>
@@ -7169,26 +7159,24 @@
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
     </row>
-    <row r="187" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A187" s="28"/>
-      <c r="B187" s="34"/>
-      <c r="C187" s="29"/>
-      <c r="D187" s="28"/>
-      <c r="E187" s="34"/>
-      <c r="F187" s="29"/>
-      <c r="G187" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="H187" s="44"/>
-      <c r="I187" s="39"/>
-      <c r="J187" s="23"/>
-      <c r="K187" s="23"/>
-      <c r="L187" s="23"/>
-      <c r="M187" s="23"/>
-      <c r="N187" s="23"/>
-      <c r="O187" s="23"/>
-      <c r="P187" s="23"/>
-      <c r="Q187" s="23"/>
+    <row r="187" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="98"/>
+      <c r="B187" s="100"/>
+      <c r="C187" s="99"/>
+      <c r="D187" s="98"/>
+      <c r="E187" s="100"/>
+      <c r="F187" s="99"/>
+      <c r="G187" s="98"/>
+      <c r="H187" s="100"/>
+      <c r="I187" s="99"/>
+      <c r="J187" s="22"/>
+      <c r="K187" s="22"/>
+      <c r="L187" s="22"/>
+      <c r="M187" s="22"/>
+      <c r="N187" s="22"/>
+      <c r="O187" s="22"/>
+      <c r="P187" s="22"/>
+      <c r="Q187" s="22"/>
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
       <c r="T187" s="1"/>
@@ -7199,26 +7187,24 @@
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
     </row>
-    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A188" s="28"/>
-      <c r="B188" s="34"/>
-      <c r="C188" s="29"/>
-      <c r="D188" s="30"/>
-      <c r="E188" s="35"/>
-      <c r="F188" s="31"/>
-      <c r="G188" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="H188" s="44"/>
-      <c r="I188" s="39"/>
-      <c r="J188" s="23"/>
-      <c r="K188" s="23"/>
-      <c r="L188" s="23"/>
-      <c r="M188" s="23"/>
-      <c r="N188" s="23"/>
-      <c r="O188" s="23"/>
-      <c r="P188" s="23"/>
-      <c r="Q188" s="23"/>
+    <row r="188" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="98"/>
+      <c r="B188" s="100"/>
+      <c r="C188" s="99"/>
+      <c r="D188" s="98"/>
+      <c r="E188" s="100"/>
+      <c r="F188" s="99"/>
+      <c r="G188" s="98"/>
+      <c r="H188" s="100"/>
+      <c r="I188" s="99"/>
+      <c r="J188" s="22"/>
+      <c r="K188" s="22"/>
+      <c r="L188" s="22"/>
+      <c r="M188" s="22"/>
+      <c r="N188" s="22"/>
+      <c r="O188" s="22"/>
+      <c r="P188" s="22"/>
+      <c r="Q188" s="22"/>
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
       <c r="T188" s="1"/>
@@ -7230,29 +7216,23 @@
       <c r="Z188" s="1"/>
     </row>
     <row r="189" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="B189" s="38"/>
-      <c r="C189" s="39"/>
-      <c r="D189" s="42" t="s">
-        <v>162</v>
-      </c>
-      <c r="E189" s="38"/>
-      <c r="F189" s="39"/>
-      <c r="G189" s="42" t="s">
-        <v>163</v>
-      </c>
-      <c r="H189" s="38"/>
-      <c r="I189" s="39"/>
-      <c r="J189" s="23"/>
-      <c r="K189" s="23"/>
-      <c r="L189" s="23"/>
-      <c r="M189" s="23"/>
-      <c r="N189" s="23"/>
-      <c r="O189" s="23"/>
-      <c r="P189" s="23"/>
-      <c r="Q189" s="23"/>
+      <c r="A189" s="98"/>
+      <c r="B189" s="100"/>
+      <c r="C189" s="99"/>
+      <c r="D189" s="98"/>
+      <c r="E189" s="100"/>
+      <c r="F189" s="99"/>
+      <c r="G189" s="98"/>
+      <c r="H189" s="100"/>
+      <c r="I189" s="99"/>
+      <c r="J189" s="22"/>
+      <c r="K189" s="22"/>
+      <c r="L189" s="22"/>
+      <c r="M189" s="22"/>
+      <c r="N189" s="22"/>
+      <c r="O189" s="22"/>
+      <c r="P189" s="22"/>
+      <c r="Q189" s="22"/>
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
       <c r="T189" s="1"/>
@@ -7264,23 +7244,23 @@
       <c r="Z189" s="1"/>
     </row>
     <row r="190" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="26"/>
-      <c r="B190" s="33"/>
-      <c r="C190" s="27"/>
-      <c r="D190" s="26"/>
-      <c r="E190" s="33"/>
-      <c r="F190" s="27"/>
-      <c r="G190" s="26"/>
-      <c r="H190" s="33"/>
-      <c r="I190" s="27"/>
-      <c r="J190" s="23"/>
-      <c r="K190" s="23"/>
-      <c r="L190" s="23"/>
-      <c r="M190" s="23"/>
-      <c r="N190" s="23"/>
-      <c r="O190" s="23"/>
-      <c r="P190" s="23"/>
-      <c r="Q190" s="23"/>
+      <c r="A190" s="98"/>
+      <c r="B190" s="100"/>
+      <c r="C190" s="99"/>
+      <c r="D190" s="98"/>
+      <c r="E190" s="100"/>
+      <c r="F190" s="99"/>
+      <c r="G190" s="98"/>
+      <c r="H190" s="100"/>
+      <c r="I190" s="99"/>
+      <c r="J190" s="22"/>
+      <c r="K190" s="22"/>
+      <c r="L190" s="22"/>
+      <c r="M190" s="22"/>
+      <c r="N190" s="22"/>
+      <c r="O190" s="22"/>
+      <c r="P190" s="22"/>
+      <c r="Q190" s="22"/>
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
       <c r="T190" s="1"/>
@@ -7292,23 +7272,23 @@
       <c r="Z190" s="1"/>
     </row>
     <row r="191" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="28"/>
-      <c r="B191" s="34"/>
-      <c r="C191" s="29"/>
-      <c r="D191" s="28"/>
-      <c r="E191" s="34"/>
-      <c r="F191" s="29"/>
-      <c r="G191" s="28"/>
-      <c r="H191" s="34"/>
-      <c r="I191" s="29"/>
-      <c r="J191" s="23"/>
-      <c r="K191" s="23"/>
-      <c r="L191" s="23"/>
-      <c r="M191" s="23"/>
-      <c r="N191" s="23"/>
-      <c r="O191" s="23"/>
-      <c r="P191" s="23"/>
-      <c r="Q191" s="23"/>
+      <c r="A191" s="98"/>
+      <c r="B191" s="100"/>
+      <c r="C191" s="99"/>
+      <c r="D191" s="98"/>
+      <c r="E191" s="100"/>
+      <c r="F191" s="99"/>
+      <c r="G191" s="98"/>
+      <c r="H191" s="100"/>
+      <c r="I191" s="99"/>
+      <c r="J191" s="22"/>
+      <c r="K191" s="22"/>
+      <c r="L191" s="22"/>
+      <c r="M191" s="22"/>
+      <c r="N191" s="22"/>
+      <c r="O191" s="22"/>
+      <c r="P191" s="22"/>
+      <c r="Q191" s="22"/>
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
       <c r="T191" s="1"/>
@@ -7320,23 +7300,23 @@
       <c r="Z191" s="1"/>
     </row>
     <row r="192" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="28"/>
-      <c r="B192" s="34"/>
-      <c r="C192" s="29"/>
-      <c r="D192" s="28"/>
-      <c r="E192" s="34"/>
-      <c r="F192" s="29"/>
-      <c r="G192" s="28"/>
-      <c r="H192" s="34"/>
-      <c r="I192" s="29"/>
-      <c r="J192" s="23"/>
-      <c r="K192" s="23"/>
-      <c r="L192" s="23"/>
-      <c r="M192" s="23"/>
-      <c r="N192" s="23"/>
-      <c r="O192" s="23"/>
-      <c r="P192" s="23"/>
-      <c r="Q192" s="23"/>
+      <c r="A192" s="98"/>
+      <c r="B192" s="100"/>
+      <c r="C192" s="99"/>
+      <c r="D192" s="98"/>
+      <c r="E192" s="100"/>
+      <c r="F192" s="99"/>
+      <c r="G192" s="98"/>
+      <c r="H192" s="100"/>
+      <c r="I192" s="99"/>
+      <c r="J192" s="22"/>
+      <c r="K192" s="22"/>
+      <c r="L192" s="22"/>
+      <c r="M192" s="22"/>
+      <c r="N192" s="22"/>
+      <c r="O192" s="22"/>
+      <c r="P192" s="22"/>
+      <c r="Q192" s="22"/>
       <c r="R192" s="1"/>
       <c r="S192" s="1"/>
       <c r="T192" s="1"/>
@@ -7348,23 +7328,23 @@
       <c r="Z192" s="1"/>
     </row>
     <row r="193" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="28"/>
-      <c r="B193" s="34"/>
-      <c r="C193" s="29"/>
-      <c r="D193" s="28"/>
-      <c r="E193" s="34"/>
-      <c r="F193" s="29"/>
-      <c r="G193" s="28"/>
-      <c r="H193" s="34"/>
-      <c r="I193" s="29"/>
-      <c r="J193" s="23"/>
-      <c r="K193" s="23"/>
-      <c r="L193" s="23"/>
-      <c r="M193" s="23"/>
-      <c r="N193" s="23"/>
-      <c r="O193" s="23"/>
-      <c r="P193" s="23"/>
-      <c r="Q193" s="23"/>
+      <c r="A193" s="98"/>
+      <c r="B193" s="100"/>
+      <c r="C193" s="99"/>
+      <c r="D193" s="98"/>
+      <c r="E193" s="100"/>
+      <c r="F193" s="99"/>
+      <c r="G193" s="98"/>
+      <c r="H193" s="100"/>
+      <c r="I193" s="99"/>
+      <c r="J193" s="22"/>
+      <c r="K193" s="22"/>
+      <c r="L193" s="22"/>
+      <c r="M193" s="22"/>
+      <c r="N193" s="22"/>
+      <c r="O193" s="22"/>
+      <c r="P193" s="22"/>
+      <c r="Q193" s="22"/>
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
       <c r="T193" s="1"/>
@@ -7376,23 +7356,23 @@
       <c r="Z193" s="1"/>
     </row>
     <row r="194" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="28"/>
-      <c r="B194" s="34"/>
-      <c r="C194" s="29"/>
-      <c r="D194" s="28"/>
-      <c r="E194" s="34"/>
-      <c r="F194" s="29"/>
-      <c r="G194" s="28"/>
-      <c r="H194" s="34"/>
-      <c r="I194" s="29"/>
-      <c r="J194" s="23"/>
-      <c r="K194" s="23"/>
-      <c r="L194" s="23"/>
-      <c r="M194" s="23"/>
-      <c r="N194" s="23"/>
-      <c r="O194" s="23"/>
-      <c r="P194" s="23"/>
-      <c r="Q194" s="23"/>
+      <c r="A194" s="98"/>
+      <c r="B194" s="100"/>
+      <c r="C194" s="99"/>
+      <c r="D194" s="98"/>
+      <c r="E194" s="100"/>
+      <c r="F194" s="99"/>
+      <c r="G194" s="98"/>
+      <c r="H194" s="100"/>
+      <c r="I194" s="99"/>
+      <c r="J194" s="22"/>
+      <c r="K194" s="22"/>
+      <c r="L194" s="22"/>
+      <c r="M194" s="22"/>
+      <c r="N194" s="22"/>
+      <c r="O194" s="22"/>
+      <c r="P194" s="22"/>
+      <c r="Q194" s="22"/>
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
       <c r="T194" s="1"/>
@@ -7404,23 +7384,23 @@
       <c r="Z194" s="1"/>
     </row>
     <row r="195" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="28"/>
-      <c r="B195" s="34"/>
-      <c r="C195" s="29"/>
-      <c r="D195" s="28"/>
-      <c r="E195" s="34"/>
-      <c r="F195" s="29"/>
-      <c r="G195" s="28"/>
-      <c r="H195" s="34"/>
-      <c r="I195" s="29"/>
-      <c r="J195" s="23"/>
-      <c r="K195" s="23"/>
-      <c r="L195" s="23"/>
-      <c r="M195" s="23"/>
-      <c r="N195" s="23"/>
-      <c r="O195" s="23"/>
-      <c r="P195" s="23"/>
-      <c r="Q195" s="23"/>
+      <c r="A195" s="98"/>
+      <c r="B195" s="100"/>
+      <c r="C195" s="99"/>
+      <c r="D195" s="98"/>
+      <c r="E195" s="100"/>
+      <c r="F195" s="99"/>
+      <c r="G195" s="98"/>
+      <c r="H195" s="100"/>
+      <c r="I195" s="99"/>
+      <c r="J195" s="22"/>
+      <c r="K195" s="22"/>
+      <c r="L195" s="22"/>
+      <c r="M195" s="22"/>
+      <c r="N195" s="22"/>
+      <c r="O195" s="22"/>
+      <c r="P195" s="22"/>
+      <c r="Q195" s="22"/>
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
       <c r="T195" s="1"/>
@@ -7432,23 +7412,23 @@
       <c r="Z195" s="1"/>
     </row>
     <row r="196" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="28"/>
-      <c r="B196" s="34"/>
-      <c r="C196" s="29"/>
-      <c r="D196" s="28"/>
-      <c r="E196" s="34"/>
-      <c r="F196" s="29"/>
-      <c r="G196" s="28"/>
-      <c r="H196" s="34"/>
-      <c r="I196" s="29"/>
-      <c r="J196" s="23"/>
-      <c r="K196" s="23"/>
-      <c r="L196" s="23"/>
-      <c r="M196" s="23"/>
-      <c r="N196" s="23"/>
-      <c r="O196" s="23"/>
-      <c r="P196" s="23"/>
-      <c r="Q196" s="23"/>
+      <c r="A196" s="98"/>
+      <c r="B196" s="100"/>
+      <c r="C196" s="99"/>
+      <c r="D196" s="98"/>
+      <c r="E196" s="100"/>
+      <c r="F196" s="99"/>
+      <c r="G196" s="98"/>
+      <c r="H196" s="100"/>
+      <c r="I196" s="99"/>
+      <c r="J196" s="22"/>
+      <c r="K196" s="22"/>
+      <c r="L196" s="22"/>
+      <c r="M196" s="22"/>
+      <c r="N196" s="22"/>
+      <c r="O196" s="22"/>
+      <c r="P196" s="22"/>
+      <c r="Q196" s="22"/>
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
       <c r="T196" s="1"/>
@@ -7460,23 +7440,23 @@
       <c r="Z196" s="1"/>
     </row>
     <row r="197" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="28"/>
-      <c r="B197" s="34"/>
-      <c r="C197" s="29"/>
-      <c r="D197" s="28"/>
-      <c r="E197" s="34"/>
-      <c r="F197" s="29"/>
-      <c r="G197" s="28"/>
-      <c r="H197" s="34"/>
-      <c r="I197" s="29"/>
-      <c r="J197" s="23"/>
-      <c r="K197" s="23"/>
-      <c r="L197" s="23"/>
-      <c r="M197" s="23"/>
-      <c r="N197" s="23"/>
-      <c r="O197" s="23"/>
-      <c r="P197" s="23"/>
-      <c r="Q197" s="23"/>
+      <c r="A197" s="98"/>
+      <c r="B197" s="100"/>
+      <c r="C197" s="99"/>
+      <c r="D197" s="98"/>
+      <c r="E197" s="100"/>
+      <c r="F197" s="99"/>
+      <c r="G197" s="98"/>
+      <c r="H197" s="100"/>
+      <c r="I197" s="99"/>
+      <c r="J197" s="22"/>
+      <c r="K197" s="22"/>
+      <c r="L197" s="22"/>
+      <c r="M197" s="22"/>
+      <c r="N197" s="22"/>
+      <c r="O197" s="22"/>
+      <c r="P197" s="22"/>
+      <c r="Q197" s="22"/>
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
       <c r="T197" s="1"/>
@@ -7488,23 +7468,23 @@
       <c r="Z197" s="1"/>
     </row>
     <row r="198" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="28"/>
-      <c r="B198" s="34"/>
-      <c r="C198" s="29"/>
-      <c r="D198" s="28"/>
-      <c r="E198" s="34"/>
-      <c r="F198" s="29"/>
-      <c r="G198" s="28"/>
-      <c r="H198" s="34"/>
-      <c r="I198" s="29"/>
-      <c r="J198" s="23"/>
-      <c r="K198" s="23"/>
-      <c r="L198" s="23"/>
-      <c r="M198" s="23"/>
-      <c r="N198" s="23"/>
-      <c r="O198" s="23"/>
-      <c r="P198" s="23"/>
-      <c r="Q198" s="23"/>
+      <c r="A198" s="98"/>
+      <c r="B198" s="100"/>
+      <c r="C198" s="99"/>
+      <c r="D198" s="98"/>
+      <c r="E198" s="100"/>
+      <c r="F198" s="99"/>
+      <c r="G198" s="98"/>
+      <c r="H198" s="100"/>
+      <c r="I198" s="99"/>
+      <c r="J198" s="22"/>
+      <c r="K198" s="22"/>
+      <c r="L198" s="22"/>
+      <c r="M198" s="22"/>
+      <c r="N198" s="22"/>
+      <c r="O198" s="22"/>
+      <c r="P198" s="22"/>
+      <c r="Q198" s="22"/>
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
       <c r="T198" s="1"/>
@@ -7516,23 +7496,23 @@
       <c r="Z198" s="1"/>
     </row>
     <row r="199" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="28"/>
-      <c r="B199" s="34"/>
-      <c r="C199" s="29"/>
-      <c r="D199" s="28"/>
-      <c r="E199" s="34"/>
-      <c r="F199" s="29"/>
-      <c r="G199" s="28"/>
-      <c r="H199" s="34"/>
-      <c r="I199" s="29"/>
-      <c r="J199" s="23"/>
-      <c r="K199" s="23"/>
-      <c r="L199" s="23"/>
-      <c r="M199" s="23"/>
-      <c r="N199" s="23"/>
-      <c r="O199" s="23"/>
-      <c r="P199" s="23"/>
-      <c r="Q199" s="23"/>
+      <c r="A199" s="98"/>
+      <c r="B199" s="100"/>
+      <c r="C199" s="99"/>
+      <c r="D199" s="98"/>
+      <c r="E199" s="100"/>
+      <c r="F199" s="99"/>
+      <c r="G199" s="98"/>
+      <c r="H199" s="100"/>
+      <c r="I199" s="99"/>
+      <c r="J199" s="22"/>
+      <c r="K199" s="22"/>
+      <c r="L199" s="22"/>
+      <c r="M199" s="22"/>
+      <c r="N199" s="22"/>
+      <c r="O199" s="22"/>
+      <c r="P199" s="22"/>
+      <c r="Q199" s="22"/>
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
       <c r="T199" s="1"/>
@@ -7544,23 +7524,23 @@
       <c r="Z199" s="1"/>
     </row>
     <row r="200" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="28"/>
-      <c r="B200" s="34"/>
-      <c r="C200" s="29"/>
-      <c r="D200" s="28"/>
-      <c r="E200" s="34"/>
-      <c r="F200" s="29"/>
-      <c r="G200" s="28"/>
-      <c r="H200" s="34"/>
-      <c r="I200" s="29"/>
-      <c r="J200" s="23"/>
-      <c r="K200" s="23"/>
-      <c r="L200" s="23"/>
-      <c r="M200" s="23"/>
-      <c r="N200" s="23"/>
-      <c r="O200" s="23"/>
-      <c r="P200" s="23"/>
-      <c r="Q200" s="23"/>
+      <c r="A200" s="98"/>
+      <c r="B200" s="100"/>
+      <c r="C200" s="99"/>
+      <c r="D200" s="98"/>
+      <c r="E200" s="100"/>
+      <c r="F200" s="99"/>
+      <c r="G200" s="98"/>
+      <c r="H200" s="100"/>
+      <c r="I200" s="99"/>
+      <c r="J200" s="22"/>
+      <c r="K200" s="22"/>
+      <c r="L200" s="22"/>
+      <c r="M200" s="22"/>
+      <c r="N200" s="22"/>
+      <c r="O200" s="22"/>
+      <c r="P200" s="22"/>
+      <c r="Q200" s="22"/>
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
       <c r="T200" s="1"/>
@@ -7572,23 +7552,23 @@
       <c r="Z200" s="1"/>
     </row>
     <row r="201" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="28"/>
-      <c r="B201" s="34"/>
-      <c r="C201" s="29"/>
-      <c r="D201" s="28"/>
-      <c r="E201" s="34"/>
-      <c r="F201" s="29"/>
-      <c r="G201" s="28"/>
-      <c r="H201" s="34"/>
-      <c r="I201" s="29"/>
-      <c r="J201" s="23"/>
-      <c r="K201" s="23"/>
-      <c r="L201" s="23"/>
-      <c r="M201" s="23"/>
-      <c r="N201" s="23"/>
-      <c r="O201" s="23"/>
-      <c r="P201" s="23"/>
-      <c r="Q201" s="23"/>
+      <c r="A201" s="98"/>
+      <c r="B201" s="100"/>
+      <c r="C201" s="99"/>
+      <c r="D201" s="101"/>
+      <c r="E201" s="103"/>
+      <c r="F201" s="102"/>
+      <c r="G201" s="101"/>
+      <c r="H201" s="103"/>
+      <c r="I201" s="102"/>
+      <c r="J201" s="22"/>
+      <c r="K201" s="22"/>
+      <c r="L201" s="22"/>
+      <c r="M201" s="22"/>
+      <c r="N201" s="22"/>
+      <c r="O201" s="22"/>
+      <c r="P201" s="22"/>
+      <c r="Q201" s="22"/>
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
       <c r="T201" s="1"/>
@@ -7600,23 +7580,29 @@
       <c r="Z201" s="1"/>
     </row>
     <row r="202" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="28"/>
-      <c r="B202" s="34"/>
-      <c r="C202" s="29"/>
-      <c r="D202" s="28"/>
-      <c r="E202" s="34"/>
-      <c r="F202" s="29"/>
-      <c r="G202" s="28"/>
-      <c r="H202" s="34"/>
-      <c r="I202" s="29"/>
-      <c r="J202" s="23"/>
-      <c r="K202" s="23"/>
-      <c r="L202" s="23"/>
-      <c r="M202" s="23"/>
-      <c r="N202" s="23"/>
-      <c r="O202" s="23"/>
-      <c r="P202" s="23"/>
-      <c r="Q202" s="23"/>
+      <c r="A202" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="B202" s="40"/>
+      <c r="C202" s="41"/>
+      <c r="D202" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="E202" s="40"/>
+      <c r="F202" s="41"/>
+      <c r="G202" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="H202" s="40"/>
+      <c r="I202" s="41"/>
+      <c r="J202" s="22"/>
+      <c r="K202" s="22"/>
+      <c r="L202" s="22"/>
+      <c r="M202" s="22"/>
+      <c r="N202" s="22"/>
+      <c r="O202" s="22"/>
+      <c r="P202" s="22"/>
+      <c r="Q202" s="22"/>
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
       <c r="T202" s="1"/>
@@ -7628,23 +7614,25 @@
       <c r="Z202" s="1"/>
     </row>
     <row r="203" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="28"/>
-      <c r="B203" s="34"/>
-      <c r="C203" s="29"/>
-      <c r="D203" s="28"/>
-      <c r="E203" s="34"/>
-      <c r="F203" s="29"/>
-      <c r="G203" s="28"/>
-      <c r="H203" s="34"/>
-      <c r="I203" s="29"/>
-      <c r="J203" s="23"/>
-      <c r="K203" s="23"/>
-      <c r="L203" s="23"/>
-      <c r="M203" s="23"/>
-      <c r="N203" s="23"/>
-      <c r="O203" s="23"/>
-      <c r="P203" s="23"/>
-      <c r="Q203" s="23"/>
+      <c r="A203" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="B203" s="40"/>
+      <c r="C203" s="40"/>
+      <c r="D203" s="40"/>
+      <c r="E203" s="40"/>
+      <c r="F203" s="40"/>
+      <c r="G203" s="40"/>
+      <c r="H203" s="40"/>
+      <c r="I203" s="41"/>
+      <c r="J203" s="22"/>
+      <c r="K203" s="22"/>
+      <c r="L203" s="22"/>
+      <c r="M203" s="22"/>
+      <c r="N203" s="22"/>
+      <c r="O203" s="22"/>
+      <c r="P203" s="22"/>
+      <c r="Q203" s="22"/>
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
       <c r="T203" s="1"/>
@@ -7656,23 +7644,23 @@
       <c r="Z203" s="1"/>
     </row>
     <row r="204" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="28"/>
-      <c r="B204" s="34"/>
-      <c r="C204" s="29"/>
-      <c r="D204" s="28"/>
-      <c r="E204" s="34"/>
-      <c r="F204" s="29"/>
-      <c r="G204" s="28"/>
-      <c r="H204" s="34"/>
-      <c r="I204" s="29"/>
-      <c r="J204" s="23"/>
-      <c r="K204" s="23"/>
-      <c r="L204" s="23"/>
-      <c r="M204" s="23"/>
-      <c r="N204" s="23"/>
-      <c r="O204" s="23"/>
-      <c r="P204" s="23"/>
-      <c r="Q204" s="23"/>
+      <c r="A204" s="75"/>
+      <c r="B204" s="40"/>
+      <c r="C204" s="40"/>
+      <c r="D204" s="40"/>
+      <c r="E204" s="40"/>
+      <c r="F204" s="40"/>
+      <c r="G204" s="40"/>
+      <c r="H204" s="40"/>
+      <c r="I204" s="41"/>
+      <c r="J204" s="22"/>
+      <c r="K204" s="22"/>
+      <c r="L204" s="22"/>
+      <c r="M204" s="22"/>
+      <c r="N204" s="22"/>
+      <c r="O204" s="22"/>
+      <c r="P204" s="22"/>
+      <c r="Q204" s="22"/>
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
       <c r="T204" s="1"/>
@@ -7684,23 +7672,23 @@
       <c r="Z204" s="1"/>
     </row>
     <row r="205" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="28"/>
-      <c r="B205" s="34"/>
-      <c r="C205" s="29"/>
-      <c r="D205" s="28"/>
-      <c r="E205" s="34"/>
-      <c r="F205" s="29"/>
-      <c r="G205" s="28"/>
-      <c r="H205" s="34"/>
-      <c r="I205" s="29"/>
-      <c r="J205" s="23"/>
-      <c r="K205" s="23"/>
-      <c r="L205" s="23"/>
-      <c r="M205" s="23"/>
-      <c r="N205" s="23"/>
-      <c r="O205" s="23"/>
-      <c r="P205" s="23"/>
-      <c r="Q205" s="23"/>
+      <c r="A205" s="74"/>
+      <c r="B205" s="40"/>
+      <c r="C205" s="40"/>
+      <c r="D205" s="40"/>
+      <c r="E205" s="40"/>
+      <c r="F205" s="40"/>
+      <c r="G205" s="40"/>
+      <c r="H205" s="40"/>
+      <c r="I205" s="41"/>
+      <c r="J205" s="22"/>
+      <c r="K205" s="22"/>
+      <c r="L205" s="22"/>
+      <c r="M205" s="22"/>
+      <c r="N205" s="22"/>
+      <c r="O205" s="22"/>
+      <c r="P205" s="22"/>
+      <c r="Q205" s="22"/>
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
       <c r="T205" s="1"/>
@@ -7712,23 +7700,23 @@
       <c r="Z205" s="1"/>
     </row>
     <row r="206" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="28"/>
-      <c r="B206" s="34"/>
-      <c r="C206" s="29"/>
-      <c r="D206" s="28"/>
-      <c r="E206" s="34"/>
-      <c r="F206" s="29"/>
-      <c r="G206" s="28"/>
-      <c r="H206" s="34"/>
-      <c r="I206" s="29"/>
-      <c r="J206" s="23"/>
-      <c r="K206" s="23"/>
-      <c r="L206" s="23"/>
-      <c r="M206" s="23"/>
-      <c r="N206" s="23"/>
-      <c r="O206" s="23"/>
-      <c r="P206" s="23"/>
-      <c r="Q206" s="23"/>
+      <c r="A206" s="74"/>
+      <c r="B206" s="40"/>
+      <c r="C206" s="40"/>
+      <c r="D206" s="40"/>
+      <c r="E206" s="40"/>
+      <c r="F206" s="40"/>
+      <c r="G206" s="40"/>
+      <c r="H206" s="40"/>
+      <c r="I206" s="41"/>
+      <c r="J206" s="22"/>
+      <c r="K206" s="22"/>
+      <c r="L206" s="22"/>
+      <c r="M206" s="22"/>
+      <c r="N206" s="22"/>
+      <c r="O206" s="22"/>
+      <c r="P206" s="22"/>
+      <c r="Q206" s="22"/>
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
       <c r="T206" s="1"/>
@@ -7740,23 +7728,23 @@
       <c r="Z206" s="1"/>
     </row>
     <row r="207" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="28"/>
-      <c r="B207" s="34"/>
-      <c r="C207" s="29"/>
-      <c r="D207" s="28"/>
-      <c r="E207" s="34"/>
-      <c r="F207" s="29"/>
-      <c r="G207" s="28"/>
-      <c r="H207" s="34"/>
-      <c r="I207" s="29"/>
-      <c r="J207" s="23"/>
-      <c r="K207" s="23"/>
-      <c r="L207" s="23"/>
-      <c r="M207" s="23"/>
-      <c r="N207" s="23"/>
-      <c r="O207" s="23"/>
-      <c r="P207" s="23"/>
-      <c r="Q207" s="23"/>
+      <c r="A207" s="74"/>
+      <c r="B207" s="40"/>
+      <c r="C207" s="40"/>
+      <c r="D207" s="40"/>
+      <c r="E207" s="40"/>
+      <c r="F207" s="40"/>
+      <c r="G207" s="40"/>
+      <c r="H207" s="40"/>
+      <c r="I207" s="41"/>
+      <c r="J207" s="22"/>
+      <c r="K207" s="22"/>
+      <c r="L207" s="22"/>
+      <c r="M207" s="22"/>
+      <c r="N207" s="22"/>
+      <c r="O207" s="22"/>
+      <c r="P207" s="22"/>
+      <c r="Q207" s="22"/>
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
       <c r="T207" s="1"/>
@@ -7768,23 +7756,23 @@
       <c r="Z207" s="1"/>
     </row>
     <row r="208" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="28"/>
-      <c r="B208" s="34"/>
-      <c r="C208" s="29"/>
-      <c r="D208" s="28"/>
-      <c r="E208" s="34"/>
-      <c r="F208" s="29"/>
-      <c r="G208" s="28"/>
-      <c r="H208" s="34"/>
-      <c r="I208" s="29"/>
-      <c r="J208" s="23"/>
-      <c r="K208" s="23"/>
-      <c r="L208" s="23"/>
-      <c r="M208" s="23"/>
-      <c r="N208" s="23"/>
-      <c r="O208" s="23"/>
-      <c r="P208" s="23"/>
-      <c r="Q208" s="23"/>
+      <c r="A208" s="75"/>
+      <c r="B208" s="40"/>
+      <c r="C208" s="40"/>
+      <c r="D208" s="40"/>
+      <c r="E208" s="40"/>
+      <c r="F208" s="40"/>
+      <c r="G208" s="40"/>
+      <c r="H208" s="40"/>
+      <c r="I208" s="41"/>
+      <c r="J208" s="22"/>
+      <c r="K208" s="22"/>
+      <c r="L208" s="22"/>
+      <c r="M208" s="22"/>
+      <c r="N208" s="22"/>
+      <c r="O208" s="22"/>
+      <c r="P208" s="22"/>
+      <c r="Q208" s="22"/>
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
       <c r="T208" s="1"/>
@@ -7796,23 +7784,25 @@
       <c r="Z208" s="1"/>
     </row>
     <row r="209" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="28"/>
-      <c r="B209" s="34"/>
-      <c r="C209" s="29"/>
-      <c r="D209" s="30"/>
-      <c r="E209" s="35"/>
-      <c r="F209" s="31"/>
-      <c r="G209" s="30"/>
-      <c r="H209" s="35"/>
-      <c r="I209" s="31"/>
-      <c r="J209" s="23"/>
-      <c r="K209" s="23"/>
-      <c r="L209" s="23"/>
-      <c r="M209" s="23"/>
-      <c r="N209" s="23"/>
-      <c r="O209" s="23"/>
-      <c r="P209" s="23"/>
-      <c r="Q209" s="23"/>
+      <c r="A209" s="73" t="s">
+        <v>159</v>
+      </c>
+      <c r="B209" s="40"/>
+      <c r="C209" s="40"/>
+      <c r="D209" s="40"/>
+      <c r="E209" s="40"/>
+      <c r="F209" s="40"/>
+      <c r="G209" s="40"/>
+      <c r="H209" s="40"/>
+      <c r="I209" s="41"/>
+      <c r="J209" s="22"/>
+      <c r="K209" s="22"/>
+      <c r="L209" s="22"/>
+      <c r="M209" s="22"/>
+      <c r="N209" s="22"/>
+      <c r="O209" s="22"/>
+      <c r="P209" s="22"/>
+      <c r="Q209" s="22"/>
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
       <c r="T209" s="1"/>
@@ -7824,29 +7814,23 @@
       <c r="Z209" s="1"/>
     </row>
     <row r="210" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="42" t="s">
-        <v>164</v>
-      </c>
-      <c r="B210" s="38"/>
-      <c r="C210" s="39"/>
-      <c r="D210" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="E210" s="38"/>
-      <c r="F210" s="39"/>
-      <c r="G210" s="42" t="s">
-        <v>166</v>
-      </c>
-      <c r="H210" s="38"/>
-      <c r="I210" s="39"/>
-      <c r="J210" s="23"/>
-      <c r="K210" s="23"/>
-      <c r="L210" s="23"/>
-      <c r="M210" s="23"/>
-      <c r="N210" s="23"/>
-      <c r="O210" s="23"/>
-      <c r="P210" s="23"/>
-      <c r="Q210" s="23"/>
+      <c r="A210" s="75"/>
+      <c r="B210" s="40"/>
+      <c r="C210" s="40"/>
+      <c r="D210" s="40"/>
+      <c r="E210" s="40"/>
+      <c r="F210" s="40"/>
+      <c r="G210" s="40"/>
+      <c r="H210" s="40"/>
+      <c r="I210" s="41"/>
+      <c r="J210" s="22"/>
+      <c r="K210" s="22"/>
+      <c r="L210" s="22"/>
+      <c r="M210" s="22"/>
+      <c r="N210" s="22"/>
+      <c r="O210" s="22"/>
+      <c r="P210" s="22"/>
+      <c r="Q210" s="22"/>
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
       <c r="T210" s="1"/>
@@ -7858,25 +7842,23 @@
       <c r="Z210" s="1"/>
     </row>
     <row r="211" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="B211" s="38"/>
-      <c r="C211" s="38"/>
-      <c r="D211" s="38"/>
-      <c r="E211" s="38"/>
-      <c r="F211" s="38"/>
-      <c r="G211" s="38"/>
-      <c r="H211" s="38"/>
-      <c r="I211" s="39"/>
-      <c r="J211" s="23"/>
-      <c r="K211" s="23"/>
-      <c r="L211" s="23"/>
-      <c r="M211" s="23"/>
-      <c r="N211" s="23"/>
-      <c r="O211" s="23"/>
-      <c r="P211" s="23"/>
-      <c r="Q211" s="23"/>
+      <c r="A211" s="75"/>
+      <c r="B211" s="40"/>
+      <c r="C211" s="40"/>
+      <c r="D211" s="40"/>
+      <c r="E211" s="40"/>
+      <c r="F211" s="40"/>
+      <c r="G211" s="40"/>
+      <c r="H211" s="40"/>
+      <c r="I211" s="41"/>
+      <c r="J211" s="22"/>
+      <c r="K211" s="22"/>
+      <c r="L211" s="22"/>
+      <c r="M211" s="22"/>
+      <c r="N211" s="22"/>
+      <c r="O211" s="22"/>
+      <c r="P211" s="22"/>
+      <c r="Q211" s="22"/>
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
       <c r="T211" s="1"/>
@@ -7888,23 +7870,23 @@
       <c r="Z211" s="1"/>
     </row>
     <row r="212" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="41"/>
-      <c r="B212" s="38"/>
-      <c r="C212" s="38"/>
-      <c r="D212" s="38"/>
-      <c r="E212" s="38"/>
-      <c r="F212" s="38"/>
-      <c r="G212" s="38"/>
-      <c r="H212" s="38"/>
-      <c r="I212" s="39"/>
-      <c r="J212" s="23"/>
-      <c r="K212" s="23"/>
-      <c r="L212" s="23"/>
-      <c r="M212" s="23"/>
-      <c r="N212" s="23"/>
-      <c r="O212" s="23"/>
-      <c r="P212" s="23"/>
-      <c r="Q212" s="23"/>
+      <c r="A212" s="75"/>
+      <c r="B212" s="40"/>
+      <c r="C212" s="40"/>
+      <c r="D212" s="40"/>
+      <c r="E212" s="40"/>
+      <c r="F212" s="40"/>
+      <c r="G212" s="40"/>
+      <c r="H212" s="40"/>
+      <c r="I212" s="41"/>
+      <c r="J212" s="1"/>
+      <c r="K212" s="1"/>
+      <c r="L212" s="1"/>
+      <c r="M212" s="1"/>
+      <c r="N212" s="1"/>
+      <c r="O212" s="1"/>
+      <c r="P212" s="1"/>
+      <c r="Q212" s="1"/>
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
       <c r="T212" s="1"/>
@@ -7916,23 +7898,23 @@
       <c r="Z212" s="1"/>
     </row>
     <row r="213" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="41"/>
-      <c r="B213" s="38"/>
-      <c r="C213" s="38"/>
-      <c r="D213" s="38"/>
-      <c r="E213" s="38"/>
-      <c r="F213" s="38"/>
-      <c r="G213" s="38"/>
-      <c r="H213" s="38"/>
-      <c r="I213" s="39"/>
-      <c r="J213" s="23"/>
-      <c r="K213" s="23"/>
-      <c r="L213" s="23"/>
-      <c r="M213" s="23"/>
-      <c r="N213" s="23"/>
-      <c r="O213" s="23"/>
-      <c r="P213" s="23"/>
-      <c r="Q213" s="23"/>
+      <c r="A213" s="75"/>
+      <c r="B213" s="40"/>
+      <c r="C213" s="40"/>
+      <c r="D213" s="40"/>
+      <c r="E213" s="40"/>
+      <c r="F213" s="40"/>
+      <c r="G213" s="40"/>
+      <c r="H213" s="40"/>
+      <c r="I213" s="41"/>
+      <c r="J213" s="1"/>
+      <c r="K213" s="1"/>
+      <c r="L213" s="1"/>
+      <c r="M213" s="1"/>
+      <c r="N213" s="1"/>
+      <c r="O213" s="1"/>
+      <c r="P213" s="1"/>
+      <c r="Q213" s="1"/>
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
       <c r="T213" s="1"/>
@@ -7944,25 +7926,23 @@
       <c r="Z213" s="1"/>
     </row>
     <row r="214" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="B214" s="38"/>
-      <c r="C214" s="38"/>
-      <c r="D214" s="38"/>
-      <c r="E214" s="38"/>
-      <c r="F214" s="38"/>
-      <c r="G214" s="38"/>
-      <c r="H214" s="38"/>
-      <c r="I214" s="39"/>
-      <c r="J214" s="23"/>
-      <c r="K214" s="23"/>
-      <c r="L214" s="23"/>
-      <c r="M214" s="23"/>
-      <c r="N214" s="23"/>
-      <c r="O214" s="23"/>
-      <c r="P214" s="23"/>
-      <c r="Q214" s="23"/>
+      <c r="A214" s="75"/>
+      <c r="B214" s="40"/>
+      <c r="C214" s="40"/>
+      <c r="D214" s="40"/>
+      <c r="E214" s="40"/>
+      <c r="F214" s="40"/>
+      <c r="G214" s="40"/>
+      <c r="H214" s="40"/>
+      <c r="I214" s="41"/>
+      <c r="J214" s="1"/>
+      <c r="K214" s="1"/>
+      <c r="L214" s="1"/>
+      <c r="M214" s="1"/>
+      <c r="N214" s="1"/>
+      <c r="O214" s="1"/>
+      <c r="P214" s="1"/>
+      <c r="Q214" s="1"/>
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
       <c r="T214" s="1"/>
@@ -7974,23 +7954,25 @@
       <c r="Z214" s="1"/>
     </row>
     <row r="215" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="41"/>
-      <c r="B215" s="38"/>
-      <c r="C215" s="38"/>
-      <c r="D215" s="38"/>
-      <c r="E215" s="38"/>
-      <c r="F215" s="38"/>
-      <c r="G215" s="38"/>
-      <c r="H215" s="38"/>
-      <c r="I215" s="39"/>
-      <c r="J215" s="23"/>
-      <c r="K215" s="23"/>
-      <c r="L215" s="23"/>
-      <c r="M215" s="23"/>
-      <c r="N215" s="23"/>
-      <c r="O215" s="23"/>
-      <c r="P215" s="23"/>
-      <c r="Q215" s="23"/>
+      <c r="A215" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="B215" s="40"/>
+      <c r="C215" s="40"/>
+      <c r="D215" s="40"/>
+      <c r="E215" s="40"/>
+      <c r="F215" s="40"/>
+      <c r="G215" s="40"/>
+      <c r="H215" s="40"/>
+      <c r="I215" s="41"/>
+      <c r="J215" s="1"/>
+      <c r="K215" s="1"/>
+      <c r="L215" s="1"/>
+      <c r="M215" s="1"/>
+      <c r="N215" s="1"/>
+      <c r="O215" s="1"/>
+      <c r="P215" s="1"/>
+      <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
       <c r="T215" s="1"/>
@@ -8002,23 +7984,23 @@
       <c r="Z215" s="1"/>
     </row>
     <row r="216" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="41"/>
-      <c r="B216" s="38"/>
-      <c r="C216" s="38"/>
-      <c r="D216" s="38"/>
-      <c r="E216" s="38"/>
-      <c r="F216" s="38"/>
-      <c r="G216" s="38"/>
-      <c r="H216" s="38"/>
-      <c r="I216" s="39"/>
-      <c r="J216" s="23"/>
-      <c r="K216" s="23"/>
-      <c r="L216" s="23"/>
-      <c r="M216" s="23"/>
-      <c r="N216" s="23"/>
-      <c r="O216" s="23"/>
-      <c r="P216" s="23"/>
-      <c r="Q216" s="23"/>
+      <c r="A216" s="74"/>
+      <c r="B216" s="40"/>
+      <c r="C216" s="40"/>
+      <c r="D216" s="40"/>
+      <c r="E216" s="40"/>
+      <c r="F216" s="40"/>
+      <c r="G216" s="40"/>
+      <c r="H216" s="40"/>
+      <c r="I216" s="41"/>
+      <c r="J216" s="1"/>
+      <c r="K216" s="1"/>
+      <c r="L216" s="1"/>
+      <c r="M216" s="1"/>
+      <c r="N216" s="1"/>
+      <c r="O216" s="1"/>
+      <c r="P216" s="1"/>
+      <c r="Q216" s="1"/>
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
       <c r="T216" s="1"/>
@@ -8030,15 +8012,15 @@
       <c r="Z216" s="1"/>
     </row>
     <row r="217" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="41"/>
-      <c r="B217" s="38"/>
-      <c r="C217" s="38"/>
-      <c r="D217" s="38"/>
-      <c r="E217" s="38"/>
-      <c r="F217" s="38"/>
-      <c r="G217" s="38"/>
-      <c r="H217" s="38"/>
-      <c r="I217" s="39"/>
+      <c r="A217" s="74"/>
+      <c r="B217" s="40"/>
+      <c r="C217" s="40"/>
+      <c r="D217" s="40"/>
+      <c r="E217" s="40"/>
+      <c r="F217" s="40"/>
+      <c r="G217" s="40"/>
+      <c r="H217" s="40"/>
+      <c r="I217" s="41"/>
       <c r="J217" s="1"/>
       <c r="K217" s="1"/>
       <c r="L217" s="1"/>
@@ -8058,15 +8040,15 @@
       <c r="Z217" s="1"/>
     </row>
     <row r="218" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="41"/>
-      <c r="B218" s="38"/>
-      <c r="C218" s="38"/>
-      <c r="D218" s="38"/>
-      <c r="E218" s="38"/>
-      <c r="F218" s="38"/>
-      <c r="G218" s="38"/>
-      <c r="H218" s="38"/>
-      <c r="I218" s="39"/>
+      <c r="A218" s="74"/>
+      <c r="B218" s="40"/>
+      <c r="C218" s="40"/>
+      <c r="D218" s="40"/>
+      <c r="E218" s="40"/>
+      <c r="F218" s="40"/>
+      <c r="G218" s="40"/>
+      <c r="H218" s="40"/>
+      <c r="I218" s="41"/>
       <c r="J218" s="1"/>
       <c r="K218" s="1"/>
       <c r="L218" s="1"/>
@@ -8086,15 +8068,15 @@
       <c r="Z218" s="1"/>
     </row>
     <row r="219" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="41"/>
-      <c r="B219" s="38"/>
-      <c r="C219" s="38"/>
-      <c r="D219" s="38"/>
-      <c r="E219" s="38"/>
-      <c r="F219" s="38"/>
-      <c r="G219" s="38"/>
-      <c r="H219" s="38"/>
-      <c r="I219" s="39"/>
+      <c r="A219" s="74"/>
+      <c r="B219" s="40"/>
+      <c r="C219" s="40"/>
+      <c r="D219" s="40"/>
+      <c r="E219" s="40"/>
+      <c r="F219" s="40"/>
+      <c r="G219" s="40"/>
+      <c r="H219" s="40"/>
+      <c r="I219" s="41"/>
       <c r="J219" s="1"/>
       <c r="K219" s="1"/>
       <c r="L219" s="1"/>
@@ -8114,17 +8096,15 @@
       <c r="Z219" s="1"/>
     </row>
     <row r="220" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="B220" s="38"/>
-      <c r="C220" s="38"/>
-      <c r="D220" s="38"/>
-      <c r="E220" s="38"/>
-      <c r="F220" s="38"/>
-      <c r="G220" s="38"/>
-      <c r="H220" s="38"/>
-      <c r="I220" s="39"/>
+      <c r="A220" s="74"/>
+      <c r="B220" s="40"/>
+      <c r="C220" s="40"/>
+      <c r="D220" s="40"/>
+      <c r="E220" s="40"/>
+      <c r="F220" s="40"/>
+      <c r="G220" s="40"/>
+      <c r="H220" s="40"/>
+      <c r="I220" s="41"/>
       <c r="J220" s="1"/>
       <c r="K220" s="1"/>
       <c r="L220" s="1"/>
@@ -8144,15 +8124,15 @@
       <c r="Z220" s="1"/>
     </row>
     <row r="221" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="40"/>
-      <c r="B221" s="38"/>
-      <c r="C221" s="38"/>
-      <c r="D221" s="38"/>
-      <c r="E221" s="38"/>
-      <c r="F221" s="38"/>
-      <c r="G221" s="38"/>
-      <c r="H221" s="38"/>
-      <c r="I221" s="39"/>
+      <c r="A221" s="1"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
+      <c r="E221" s="1"/>
+      <c r="F221" s="1"/>
+      <c r="G221" s="1"/>
+      <c r="H221" s="1"/>
+      <c r="I221" s="1"/>
       <c r="J221" s="1"/>
       <c r="K221" s="1"/>
       <c r="L221" s="1"/>
@@ -8172,15 +8152,15 @@
       <c r="Z221" s="1"/>
     </row>
     <row r="222" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="40"/>
-      <c r="B222" s="38"/>
-      <c r="C222" s="38"/>
-      <c r="D222" s="38"/>
-      <c r="E222" s="38"/>
-      <c r="F222" s="38"/>
-      <c r="G222" s="38"/>
-      <c r="H222" s="38"/>
-      <c r="I222" s="39"/>
+      <c r="A222" s="1"/>
+      <c r="B222" s="1"/>
+      <c r="C222" s="1"/>
+      <c r="D222" s="1"/>
+      <c r="E222" s="1"/>
+      <c r="F222" s="1"/>
+      <c r="G222" s="1"/>
+      <c r="H222" s="1"/>
+      <c r="I222" s="1"/>
       <c r="J222" s="1"/>
       <c r="K222" s="1"/>
       <c r="L222" s="1"/>
@@ -8200,15 +8180,15 @@
       <c r="Z222" s="1"/>
     </row>
     <row r="223" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="40"/>
-      <c r="B223" s="38"/>
-      <c r="C223" s="38"/>
-      <c r="D223" s="38"/>
-      <c r="E223" s="38"/>
-      <c r="F223" s="38"/>
-      <c r="G223" s="38"/>
-      <c r="H223" s="38"/>
-      <c r="I223" s="39"/>
+      <c r="A223" s="1"/>
+      <c r="B223" s="1"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1"/>
+      <c r="E223" s="1"/>
+      <c r="F223" s="1"/>
+      <c r="G223" s="1"/>
+      <c r="H223" s="1"/>
+      <c r="I223" s="1"/>
       <c r="J223" s="1"/>
       <c r="K223" s="1"/>
       <c r="L223" s="1"/>
@@ -15591,131 +15571,132 @@
       <c r="Y486" s="1"/>
       <c r="Z486" s="1"/>
     </row>
-    <row r="487" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A487" s="1"/>
-      <c r="B487" s="1"/>
-      <c r="C487" s="1"/>
-      <c r="D487" s="1"/>
-      <c r="E487" s="1"/>
-      <c r="F487" s="1"/>
-      <c r="G487" s="1"/>
-      <c r="H487" s="1"/>
-      <c r="I487" s="1"/>
-      <c r="J487" s="1"/>
-      <c r="K487" s="1"/>
-      <c r="L487" s="1"/>
-      <c r="M487" s="1"/>
-      <c r="N487" s="1"/>
-      <c r="O487" s="1"/>
-      <c r="P487" s="1"/>
-      <c r="Q487" s="1"/>
-      <c r="R487" s="1"/>
-      <c r="S487" s="1"/>
-      <c r="T487" s="1"/>
-      <c r="U487" s="1"/>
-      <c r="V487" s="1"/>
-      <c r="W487" s="1"/>
-      <c r="X487" s="1"/>
-      <c r="Y487" s="1"/>
-      <c r="Z487" s="1"/>
-    </row>
-    <row r="488" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A488" s="1"/>
-      <c r="B488" s="1"/>
-      <c r="C488" s="1"/>
-      <c r="D488" s="1"/>
-      <c r="E488" s="1"/>
-      <c r="F488" s="1"/>
-      <c r="G488" s="1"/>
-      <c r="H488" s="1"/>
-      <c r="I488" s="1"/>
-      <c r="J488" s="1"/>
-      <c r="K488" s="1"/>
-      <c r="L488" s="1"/>
-      <c r="M488" s="1"/>
-      <c r="N488" s="1"/>
-      <c r="O488" s="1"/>
-      <c r="P488" s="1"/>
-      <c r="Q488" s="1"/>
-      <c r="R488" s="1"/>
-      <c r="S488" s="1"/>
-      <c r="T488" s="1"/>
-      <c r="U488" s="1"/>
-      <c r="V488" s="1"/>
-      <c r="W488" s="1"/>
-      <c r="X488" s="1"/>
-      <c r="Y488" s="1"/>
-      <c r="Z488" s="1"/>
-    </row>
-    <row r="489" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A489" s="1"/>
-      <c r="B489" s="1"/>
-      <c r="C489" s="1"/>
-      <c r="D489" s="1"/>
-      <c r="E489" s="1"/>
-      <c r="F489" s="1"/>
-      <c r="G489" s="1"/>
-      <c r="H489" s="1"/>
-      <c r="I489" s="1"/>
-      <c r="J489" s="1"/>
-      <c r="K489" s="1"/>
-      <c r="L489" s="1"/>
-      <c r="M489" s="1"/>
-      <c r="N489" s="1"/>
-      <c r="O489" s="1"/>
-      <c r="P489" s="1"/>
-      <c r="Q489" s="1"/>
-      <c r="R489" s="1"/>
-      <c r="S489" s="1"/>
-      <c r="T489" s="1"/>
-      <c r="U489" s="1"/>
-      <c r="V489" s="1"/>
-      <c r="W489" s="1"/>
-      <c r="X489" s="1"/>
-      <c r="Y489" s="1"/>
-      <c r="Z489" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="172">
-    <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A3:B11"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="A13:B17"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="E19:E33"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D33"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I33"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="B39:I39"/>
-    <mergeCell ref="B40:I40"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A43:H43"/>
+  <mergeCells count="173">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="A218:I218"/>
+    <mergeCell ref="A217:I217"/>
+    <mergeCell ref="A207:I207"/>
+    <mergeCell ref="A206:I206"/>
+    <mergeCell ref="A205:I205"/>
+    <mergeCell ref="A215:I215"/>
+    <mergeCell ref="A216:I216"/>
+    <mergeCell ref="A219:I219"/>
+    <mergeCell ref="A220:I220"/>
+    <mergeCell ref="A203:I203"/>
+    <mergeCell ref="A204:I204"/>
+    <mergeCell ref="A208:I208"/>
+    <mergeCell ref="A209:I209"/>
+    <mergeCell ref="A210:I210"/>
+    <mergeCell ref="A211:I211"/>
+    <mergeCell ref="A212:I212"/>
+    <mergeCell ref="A213:I213"/>
+    <mergeCell ref="A214:I214"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="D181:F181"/>
+    <mergeCell ref="G181:I181"/>
+    <mergeCell ref="A202:C202"/>
+    <mergeCell ref="D202:F202"/>
+    <mergeCell ref="G202:I202"/>
+    <mergeCell ref="A160:I160"/>
+    <mergeCell ref="H178:I178"/>
+    <mergeCell ref="H179:I179"/>
+    <mergeCell ref="H180:I180"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="H132:I132"/>
+    <mergeCell ref="A147:B147"/>
+    <mergeCell ref="C147:D147"/>
+    <mergeCell ref="E147:G147"/>
+    <mergeCell ref="H147:I147"/>
+    <mergeCell ref="G116:I116"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="G117:I117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="G118:I118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="G119:I119"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="H102:I102"/>
+    <mergeCell ref="A103:I103"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="D104:E119"/>
+    <mergeCell ref="F104:I104"/>
+    <mergeCell ref="F107:I107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="H108:I108"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="H109:I109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="F110:I110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:I111"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="G112:I112"/>
+    <mergeCell ref="G113:I113"/>
+    <mergeCell ref="G114:I114"/>
+    <mergeCell ref="G115:I115"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="F97:I97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="A89:H89"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A93:H93"/>
+    <mergeCell ref="A94:H94"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:I95"/>
+    <mergeCell ref="A96:I96"/>
+    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="A82:H82"/>
+    <mergeCell ref="A83:H83"/>
+    <mergeCell ref="A84:H84"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A88:H88"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A61:H61"/>
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="A45:H45"/>
     <mergeCell ref="A46:H46"/>
@@ -15725,134 +15706,50 @@
     <mergeCell ref="A50:H50"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A73:H73"/>
-    <mergeCell ref="A74:H74"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A76:H76"/>
-    <mergeCell ref="A77:H77"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="A81:H81"/>
-    <mergeCell ref="A82:H82"/>
-    <mergeCell ref="A83:H83"/>
-    <mergeCell ref="A84:H84"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A86:H86"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A89:H89"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A91:H91"/>
-    <mergeCell ref="A92:H92"/>
-    <mergeCell ref="A93:H93"/>
-    <mergeCell ref="A94:H94"/>
-    <mergeCell ref="A95:H95"/>
-    <mergeCell ref="A96:H96"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A98:H98"/>
-    <mergeCell ref="A99:H99"/>
-    <mergeCell ref="A100:H100"/>
-    <mergeCell ref="A101:H101"/>
-    <mergeCell ref="A102:H102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:I103"/>
-    <mergeCell ref="A104:I104"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="C105:E105"/>
-    <mergeCell ref="F105:I105"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="G106:H106"/>
-    <mergeCell ref="E106:E109"/>
-    <mergeCell ref="G107:H107"/>
-    <mergeCell ref="G108:H108"/>
-    <mergeCell ref="G109:H109"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="F110:G110"/>
-    <mergeCell ref="H110:I110"/>
-    <mergeCell ref="A111:I111"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="D112:E127"/>
-    <mergeCell ref="F112:I112"/>
-    <mergeCell ref="F115:I115"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="H116:I116"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="H117:I117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="F118:I118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="F119:I119"/>
-    <mergeCell ref="A120:C120"/>
-    <mergeCell ref="G120:I120"/>
-    <mergeCell ref="G121:I121"/>
-    <mergeCell ref="G122:I122"/>
-    <mergeCell ref="G123:I123"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A140:B140"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="E140:G140"/>
-    <mergeCell ref="H140:I140"/>
-    <mergeCell ref="A155:B155"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="E155:G155"/>
-    <mergeCell ref="H155:I155"/>
-    <mergeCell ref="G124:I124"/>
-    <mergeCell ref="A125:C125"/>
-    <mergeCell ref="G125:I125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="G127:I127"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="D189:F189"/>
-    <mergeCell ref="G189:I189"/>
-    <mergeCell ref="A210:C210"/>
-    <mergeCell ref="D210:F210"/>
-    <mergeCell ref="G210:I210"/>
-    <mergeCell ref="A168:I168"/>
-    <mergeCell ref="H186:I186"/>
-    <mergeCell ref="H187:I187"/>
-    <mergeCell ref="H188:I188"/>
-    <mergeCell ref="A220:I220"/>
-    <mergeCell ref="A221:I221"/>
-    <mergeCell ref="A222:I222"/>
-    <mergeCell ref="A223:I223"/>
-    <mergeCell ref="A211:I211"/>
-    <mergeCell ref="A212:I212"/>
-    <mergeCell ref="A213:I213"/>
-    <mergeCell ref="A214:I214"/>
-    <mergeCell ref="A215:I215"/>
-    <mergeCell ref="A216:I216"/>
-    <mergeCell ref="A217:I217"/>
-    <mergeCell ref="A218:I218"/>
-    <mergeCell ref="A219:I219"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="E11:E25"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H24:I25"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>